--- a/research/traditional_assets/database/data/finland/finland_transportation.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_transportation.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08567392956617489</v>
+        <v>0.08553858170704254</v>
       </c>
       <c r="C2">
-        <v>108.9394596922095</v>
+        <v>107.9023247773597</v>
       </c>
       <c r="D2">
-        <v>102.9994596922095</v>
+        <v>103.0580356486408</v>
       </c>
       <c r="E2">
-        <v>-24.97108712810374</v>
+        <v>-23.8753762568227</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.095710871281037</v>
       </c>
       <c r="G2">
         <v>5.94</v>
@@ -1439,28 +1439,28 @@
         <v>23.624</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.05511425682543617</v>
       </c>
       <c r="N2">
-        <v>23.624</v>
+        <v>23.56888574317457</v>
       </c>
       <c r="O2">
-        <v>4.724800000000001</v>
+        <v>4.713777148634914</v>
       </c>
       <c r="P2">
-        <v>18.8992</v>
+        <v>18.85510859453965</v>
       </c>
       <c r="Q2">
-        <v>24.8292</v>
+        <v>24.78510859453965</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08567392956617489</v>
+        <v>0.08599614313842681</v>
       </c>
       <c r="T2">
-        <v>0.8198499599185859</v>
+        <v>0.8264750100997462</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>428.636823949645</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08553858170704254</v>
+        <v>0.08540323384791018</v>
       </c>
       <c r="C3">
-        <v>107.9023247773597</v>
+        <v>106.8652565249</v>
       </c>
       <c r="D3">
-        <v>103.0580356486408</v>
+        <v>103.1166782674621</v>
       </c>
       <c r="E3">
-        <v>-23.8753762568227</v>
+        <v>-22.77966538554166</v>
       </c>
       <c r="F3">
-        <v>1.095710871281037</v>
+        <v>2.191421742562075</v>
       </c>
       <c r="G3">
         <v>5.94</v>
@@ -1521,28 +1521,28 @@
         <v>23.624</v>
       </c>
       <c r="M3">
-        <v>0.05511425682543617</v>
+        <v>0.1102285136508723</v>
       </c>
       <c r="N3">
-        <v>23.56888574317457</v>
+        <v>23.51377148634913</v>
       </c>
       <c r="O3">
-        <v>4.713777148634914</v>
+        <v>4.702754297269826</v>
       </c>
       <c r="P3">
-        <v>18.85510859453965</v>
+        <v>18.8110171890793</v>
       </c>
       <c r="Q3">
-        <v>24.78510859453965</v>
+        <v>24.7410171890793</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08599614313842681</v>
+        <v>0.08632493249786755</v>
       </c>
       <c r="T3">
-        <v>0.8264750100997462</v>
+        <v>0.8332352653866444</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>428.636823949645</v>
+        <v>214.3184119748225</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08540323384791018</v>
+        <v>0.08526788598877784</v>
       </c>
       <c r="C4">
-        <v>106.8652565249</v>
+        <v>105.8282550486928</v>
       </c>
       <c r="D4">
-        <v>103.1166782674621</v>
+        <v>103.175387662536</v>
       </c>
       <c r="E4">
-        <v>-22.77966538554166</v>
+        <v>-21.68395451426062</v>
       </c>
       <c r="F4">
-        <v>2.191421742562075</v>
+        <v>3.287132613843112</v>
       </c>
       <c r="G4">
         <v>5.94</v>
@@ -1603,28 +1603,28 @@
         <v>23.624</v>
       </c>
       <c r="M4">
-        <v>0.1102285136508723</v>
+        <v>0.1653427704763085</v>
       </c>
       <c r="N4">
-        <v>23.51377148634913</v>
+        <v>23.45865722952369</v>
       </c>
       <c r="O4">
-        <v>4.702754297269826</v>
+        <v>4.691731445904739</v>
       </c>
       <c r="P4">
-        <v>18.8110171890793</v>
+        <v>18.76692578361896</v>
       </c>
       <c r="Q4">
-        <v>24.7410171890793</v>
+        <v>24.69692578361895</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08632493249786755</v>
+        <v>0.0866605010193586</v>
       </c>
       <c r="T4">
-        <v>0.8332352653866444</v>
+        <v>0.840134907380489</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>214.3184119748225</v>
+        <v>142.8789413165483</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08526788598877784</v>
+        <v>0.0851325381296455</v>
       </c>
       <c r="C5">
-        <v>105.8282550486928</v>
+        <v>104.7913204628602</v>
       </c>
       <c r="D5">
-        <v>103.175387662536</v>
+        <v>103.2341639479844</v>
       </c>
       <c r="E5">
-        <v>-21.68395451426062</v>
+        <v>-20.58824364297959</v>
       </c>
       <c r="F5">
-        <v>3.287132613843112</v>
+        <v>4.382843485124149</v>
       </c>
       <c r="G5">
         <v>5.94</v>
@@ -1685,28 +1685,28 @@
         <v>23.624</v>
       </c>
       <c r="M5">
-        <v>0.1653427704763085</v>
+        <v>0.2204570273017447</v>
       </c>
       <c r="N5">
-        <v>23.45865722952369</v>
+        <v>23.40354297269826</v>
       </c>
       <c r="O5">
-        <v>4.691731445904739</v>
+        <v>4.680708594539651</v>
       </c>
       <c r="P5">
-        <v>18.76692578361896</v>
+        <v>18.72283437815861</v>
       </c>
       <c r="Q5">
-        <v>24.69692578361895</v>
+        <v>24.65283437815861</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0866605010193586</v>
+        <v>0.08700306055171406</v>
       </c>
       <c r="T5">
-        <v>0.840134907380489</v>
+        <v>0.8471782919158721</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>142.8789413165483</v>
+        <v>107.1592059874112</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0851325381296455</v>
+        <v>0.08499719027051313</v>
       </c>
       <c r="C6">
-        <v>104.7913204628602</v>
+        <v>103.7544528817844</v>
       </c>
       <c r="D6">
-        <v>103.2341639479844</v>
+        <v>103.2930072381896</v>
       </c>
       <c r="E6">
-        <v>-20.58824364297959</v>
+        <v>-19.49253277169855</v>
       </c>
       <c r="F6">
-        <v>4.382843485124149</v>
+        <v>5.478554356405187</v>
       </c>
       <c r="G6">
         <v>5.94</v>
@@ -1767,28 +1767,28 @@
         <v>23.624</v>
       </c>
       <c r="M6">
-        <v>0.2204570273017447</v>
+        <v>0.2755712841271809</v>
       </c>
       <c r="N6">
-        <v>23.40354297269826</v>
+        <v>23.34842871587282</v>
       </c>
       <c r="O6">
-        <v>4.680708594539651</v>
+        <v>4.669685743174564</v>
       </c>
       <c r="P6">
-        <v>18.72283437815861</v>
+        <v>18.67874297269826</v>
       </c>
       <c r="Q6">
-        <v>24.65283437815861</v>
+        <v>24.60874297269826</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08700306055171406</v>
+        <v>0.08735283186369804</v>
       </c>
       <c r="T6">
-        <v>0.8471782919158721</v>
+        <v>0.8543699582309473</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>107.1592059874112</v>
+        <v>85.72736478992897</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08499719027051313</v>
+        <v>0.08486184241138078</v>
       </c>
       <c r="C7">
-        <v>103.7544528817844</v>
+        <v>102.7176524201084</v>
       </c>
       <c r="D7">
-        <v>103.2930072381896</v>
+        <v>103.3519176477947</v>
       </c>
       <c r="E7">
-        <v>-19.49253277169855</v>
+        <v>-18.39682190041751</v>
       </c>
       <c r="F7">
-        <v>5.478554356405187</v>
+        <v>6.574265227686224</v>
       </c>
       <c r="G7">
         <v>5.94</v>
@@ -1849,28 +1849,28 @@
         <v>23.624</v>
       </c>
       <c r="M7">
-        <v>0.2755712841271809</v>
+        <v>0.330685540952617</v>
       </c>
       <c r="N7">
-        <v>23.34842871587282</v>
+        <v>23.29331445904738</v>
       </c>
       <c r="O7">
-        <v>4.669685743174564</v>
+        <v>4.658662891809477</v>
       </c>
       <c r="P7">
-        <v>18.67874297269826</v>
+        <v>18.63465156723791</v>
       </c>
       <c r="Q7">
-        <v>24.60874297269826</v>
+        <v>24.56465156723791</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08735283186369804</v>
+        <v>0.0877100451184902</v>
       </c>
       <c r="T7">
-        <v>0.8543699582309473</v>
+        <v>0.8617146387229393</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>85.72736478992897</v>
+        <v>71.43947065827415</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08486184241138078</v>
+        <v>0.08472649455224844</v>
       </c>
       <c r="C8">
-        <v>102.7176524201084</v>
+        <v>101.6809191927372</v>
       </c>
       <c r="D8">
-        <v>103.3519176477947</v>
+        <v>103.4108952917044</v>
       </c>
       <c r="E8">
-        <v>-18.39682190041751</v>
+        <v>-17.30111102913648</v>
       </c>
       <c r="F8">
-        <v>6.574265227686223</v>
+        <v>7.66997609896726</v>
       </c>
       <c r="G8">
         <v>5.94</v>
@@ -1931,28 +1931,28 @@
         <v>23.624</v>
       </c>
       <c r="M8">
-        <v>0.330685540952617</v>
+        <v>0.3857997977780532</v>
       </c>
       <c r="N8">
-        <v>23.29331445904738</v>
+        <v>23.23820020222195</v>
       </c>
       <c r="O8">
-        <v>4.658662891809477</v>
+        <v>4.64764004044439</v>
       </c>
       <c r="P8">
-        <v>18.63465156723791</v>
+        <v>18.59056016177756</v>
       </c>
       <c r="Q8">
-        <v>24.56465156723791</v>
+        <v>24.52056016177756</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0877100451184902</v>
+        <v>0.08807494037876176</v>
       </c>
       <c r="T8">
-        <v>0.8617146387229393</v>
+        <v>0.8692172693330384</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>71.43947065827416</v>
+        <v>61.23383199280643</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08472649455224843</v>
+        <v>0.0845911466931161</v>
       </c>
       <c r="C9">
-        <v>101.6809191927372</v>
+        <v>100.6442533148378</v>
       </c>
       <c r="D9">
-        <v>103.4108952917044</v>
+        <v>103.4699402850861</v>
       </c>
       <c r="E9">
-        <v>-17.30111102913648</v>
+        <v>-16.20540015785544</v>
       </c>
       <c r="F9">
-        <v>7.669976098967262</v>
+        <v>8.765686970248298</v>
       </c>
       <c r="G9">
         <v>5.94</v>
@@ -2013,28 +2013,28 @@
         <v>23.624</v>
       </c>
       <c r="M9">
-        <v>0.3857997977780533</v>
+        <v>0.4409140546034894</v>
       </c>
       <c r="N9">
-        <v>23.23820020222195</v>
+        <v>23.18308594539651</v>
       </c>
       <c r="O9">
-        <v>4.64764004044439</v>
+        <v>4.636617189079303</v>
       </c>
       <c r="P9">
-        <v>18.59056016177756</v>
+        <v>18.54646875631721</v>
       </c>
       <c r="Q9">
-        <v>24.52056016177756</v>
+        <v>24.47646875631721</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08807494037876176</v>
+        <v>0.08844776814469141</v>
       </c>
       <c r="T9">
-        <v>0.8692172693330384</v>
+        <v>0.8768830006085745</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>61.23383199280642</v>
+        <v>53.57960299370562</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0845911466931161</v>
+        <v>0.08445579883398374</v>
       </c>
       <c r="C10">
-        <v>100.6442533148378</v>
+        <v>99.60765490184073</v>
       </c>
       <c r="D10">
-        <v>103.4699402850861</v>
+        <v>103.5290527433701</v>
       </c>
       <c r="E10">
-        <v>-16.20540015785544</v>
+        <v>-15.1096892865744</v>
       </c>
       <c r="F10">
-        <v>8.765686970248298</v>
+        <v>9.861397841529335</v>
       </c>
       <c r="G10">
         <v>5.94</v>
@@ -2095,28 +2095,28 @@
         <v>23.624</v>
       </c>
       <c r="M10">
-        <v>0.4409140546034894</v>
+        <v>0.4960283114289256</v>
       </c>
       <c r="N10">
-        <v>23.18308594539651</v>
+        <v>23.12797168857108</v>
       </c>
       <c r="O10">
-        <v>4.636617189079303</v>
+        <v>4.625594337714215</v>
       </c>
       <c r="P10">
-        <v>18.54646875631721</v>
+        <v>18.50237735085686</v>
       </c>
       <c r="Q10">
-        <v>24.47646875631721</v>
+        <v>24.43237735085686</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08844776814469141</v>
+        <v>0.08882878992745466</v>
       </c>
       <c r="T10">
-        <v>0.8768830006085745</v>
+        <v>0.8847172094945619</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>53.57960299370562</v>
+        <v>47.62631377218277</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08445579883398374</v>
+        <v>0.0843204509748514</v>
       </c>
       <c r="C11">
-        <v>99.60765490184073</v>
+        <v>98.57112406944042</v>
       </c>
       <c r="D11">
-        <v>103.5290527433701</v>
+        <v>103.5882327822508</v>
       </c>
       <c r="E11">
-        <v>-15.1096892865744</v>
+        <v>-14.01397841529336</v>
       </c>
       <c r="F11">
-        <v>9.861397841529335</v>
+        <v>10.95710871281037</v>
       </c>
       <c r="G11">
         <v>5.94</v>
@@ -2177,28 +2177,28 @@
         <v>23.624</v>
       </c>
       <c r="M11">
-        <v>0.4960283114289256</v>
+        <v>0.5511425682543617</v>
       </c>
       <c r="N11">
-        <v>23.12797168857108</v>
+        <v>23.07285743174564</v>
       </c>
       <c r="O11">
-        <v>4.625594337714215</v>
+        <v>4.614571486349128</v>
       </c>
       <c r="P11">
-        <v>18.50237735085686</v>
+        <v>18.45828594539651</v>
       </c>
       <c r="Q11">
-        <v>24.43237735085686</v>
+        <v>24.38828594539651</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08882878992745466</v>
+        <v>0.08921827886094599</v>
       </c>
       <c r="T11">
-        <v>0.8847172094945619</v>
+        <v>0.892725511911349</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>47.62631377218277</v>
+        <v>42.86368239496449</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0843204509748514</v>
+        <v>0.08418510311571904</v>
       </c>
       <c r="C12">
-        <v>98.5711240694404</v>
+        <v>97.53466093359579</v>
       </c>
       <c r="D12">
-        <v>103.5882327822508</v>
+        <v>103.6474805176872</v>
       </c>
       <c r="E12">
-        <v>-14.01397841529336</v>
+        <v>-12.91826754401233</v>
       </c>
       <c r="F12">
-        <v>10.95710871281037</v>
+        <v>12.05281958409141</v>
       </c>
       <c r="G12">
         <v>5.94</v>
@@ -2259,28 +2259,28 @@
         <v>23.624</v>
       </c>
       <c r="M12">
-        <v>0.5511425682543618</v>
+        <v>0.6062568250797978</v>
       </c>
       <c r="N12">
-        <v>23.07285743174564</v>
+        <v>23.01774317492021</v>
       </c>
       <c r="O12">
-        <v>4.614571486349128</v>
+        <v>4.603548634984041</v>
       </c>
       <c r="P12">
-        <v>18.45828594539651</v>
+        <v>18.41419453993617</v>
       </c>
       <c r="Q12">
-        <v>24.38828594539651</v>
+        <v>24.34419453993617</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08921827886094599</v>
+        <v>0.08961652035474049</v>
       </c>
       <c r="T12">
-        <v>0.8927255119113492</v>
+        <v>0.9009137761801989</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>42.86368239496448</v>
+        <v>38.96698399542228</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08418510311571904</v>
+        <v>0.08404975525658669</v>
       </c>
       <c r="C13">
-        <v>97.53466093359579</v>
+        <v>96.49826561053139</v>
       </c>
       <c r="D13">
-        <v>103.6474805176872</v>
+        <v>103.7067960659038</v>
       </c>
       <c r="E13">
-        <v>-12.91826754401233</v>
+        <v>-11.82255667273129</v>
       </c>
       <c r="F13">
-        <v>12.05281958409141</v>
+        <v>13.14853045537245</v>
       </c>
       <c r="G13">
         <v>5.94</v>
@@ -2341,28 +2341,28 @@
         <v>23.624</v>
       </c>
       <c r="M13">
-        <v>0.6062568250797978</v>
+        <v>0.661371081905234</v>
       </c>
       <c r="N13">
-        <v>23.01774317492021</v>
+        <v>22.96262891809477</v>
       </c>
       <c r="O13">
-        <v>4.603548634984041</v>
+        <v>4.592525783618954</v>
       </c>
       <c r="P13">
-        <v>18.41419453993617</v>
+        <v>18.37010313447582</v>
       </c>
       <c r="Q13">
-        <v>24.34419453993617</v>
+        <v>24.30010313447582</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08961652035474049</v>
+        <v>0.09002381279157579</v>
       </c>
       <c r="T13">
-        <v>0.9009137761801989</v>
+        <v>0.9092881373642498</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>38.96698399542228</v>
+        <v>35.71973532913709</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08404975525658669</v>
+        <v>0.08391440739745436</v>
       </c>
       <c r="C14">
-        <v>96.49826561053139</v>
+        <v>95.46193821673789</v>
       </c>
       <c r="D14">
-        <v>103.7067960659038</v>
+        <v>103.7661795433914</v>
       </c>
       <c r="E14">
-        <v>-11.82255667273129</v>
+        <v>-10.72684580145025</v>
       </c>
       <c r="F14">
-        <v>13.14853045537245</v>
+        <v>14.24424132665349</v>
       </c>
       <c r="G14">
         <v>5.94</v>
@@ -2423,28 +2423,28 @@
         <v>23.624</v>
       </c>
       <c r="M14">
-        <v>0.661371081905234</v>
+        <v>0.7164853387306703</v>
       </c>
       <c r="N14">
-        <v>22.96262891809477</v>
+        <v>22.90751466126933</v>
       </c>
       <c r="O14">
-        <v>4.592525783618954</v>
+        <v>4.581502932253867</v>
       </c>
       <c r="P14">
-        <v>18.37010313447582</v>
+        <v>18.32601172901547</v>
       </c>
       <c r="Q14">
-        <v>24.30010313447582</v>
+        <v>24.25601172901547</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09002381279157579</v>
+        <v>0.09044046827293603</v>
       </c>
       <c r="T14">
-        <v>0.9092881373642498</v>
+        <v>0.9178550125985088</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>35.71973532913709</v>
+        <v>32.97206338074191</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08391440739745436</v>
+        <v>0.083779059538322</v>
       </c>
       <c r="C15">
-        <v>95.46193821673789</v>
+        <v>94.42567886897295</v>
       </c>
       <c r="D15">
-        <v>103.7661795433914</v>
+        <v>103.8256310669075</v>
       </c>
       <c r="E15">
-        <v>-10.72684580145025</v>
+        <v>-9.631134930169212</v>
       </c>
       <c r="F15">
-        <v>14.24424132665349</v>
+        <v>15.33995219793452</v>
       </c>
       <c r="G15">
         <v>5.94</v>
@@ -2505,28 +2505,28 @@
         <v>23.624</v>
       </c>
       <c r="M15">
-        <v>0.7164853387306703</v>
+        <v>0.7715995955561066</v>
       </c>
       <c r="N15">
-        <v>22.90751466126933</v>
+        <v>22.85240040444389</v>
       </c>
       <c r="O15">
-        <v>4.581502932253867</v>
+        <v>4.570480080888779</v>
       </c>
       <c r="P15">
-        <v>18.32601172901547</v>
+        <v>18.28192032355512</v>
       </c>
       <c r="Q15">
-        <v>24.25601172901547</v>
+        <v>24.21192032355512</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09044046827293603</v>
+        <v>0.09086681341665348</v>
       </c>
       <c r="T15">
-        <v>0.9178550125985088</v>
+        <v>0.9266211174893785</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>32.97206338074191</v>
+        <v>30.6169159964032</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.083779059538322</v>
+        <v>0.08364371167918964</v>
       </c>
       <c r="C16">
-        <v>94.42567886897295</v>
+        <v>93.38948768426195</v>
       </c>
       <c r="D16">
-        <v>103.8256310669075</v>
+        <v>103.8851507534775</v>
       </c>
       <c r="E16">
-        <v>-9.631134930169212</v>
+        <v>-8.535424058888175</v>
       </c>
       <c r="F16">
-        <v>15.33995219793452</v>
+        <v>16.43566306921556</v>
       </c>
       <c r="G16">
         <v>5.94</v>
@@ -2587,28 +2587,28 @@
         <v>23.624</v>
       </c>
       <c r="M16">
-        <v>0.7715995955561066</v>
+        <v>0.8267138523815427</v>
       </c>
       <c r="N16">
-        <v>22.85240040444389</v>
+        <v>22.79728614761846</v>
       </c>
       <c r="O16">
-        <v>4.570480080888779</v>
+        <v>4.559457229523693</v>
       </c>
       <c r="P16">
-        <v>18.28192032355512</v>
+        <v>18.23782891809477</v>
       </c>
       <c r="Q16">
-        <v>24.21192032355512</v>
+        <v>24.16782891809477</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09086681341665348</v>
+        <v>0.09130319021081135</v>
       </c>
       <c r="T16">
-        <v>0.9266211174893785</v>
+        <v>0.935593483671798</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>30.6169159964032</v>
+        <v>28.57578826330966</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08364371167918964</v>
+        <v>0.08350836382005729</v>
       </c>
       <c r="C17">
-        <v>93.38948768426195</v>
+        <v>92.35336477989881</v>
       </c>
       <c r="D17">
-        <v>103.8851507534775</v>
+        <v>103.9447387203954</v>
       </c>
       <c r="E17">
-        <v>-8.535424058888179</v>
+        <v>-7.43971318760714</v>
       </c>
       <c r="F17">
-        <v>16.43566306921556</v>
+        <v>17.5313739404966</v>
       </c>
       <c r="G17">
         <v>5.94</v>
@@ -2669,28 +2669,28 @@
         <v>23.624</v>
       </c>
       <c r="M17">
-        <v>0.8267138523815425</v>
+        <v>0.8818281092069787</v>
       </c>
       <c r="N17">
-        <v>22.79728614761846</v>
+        <v>22.74217189079302</v>
       </c>
       <c r="O17">
-        <v>4.559457229523693</v>
+        <v>4.548434378158605</v>
       </c>
       <c r="P17">
-        <v>18.23782891809477</v>
+        <v>18.19373751263442</v>
       </c>
       <c r="Q17">
-        <v>24.16782891809477</v>
+        <v>24.12373751263442</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09130319021081135</v>
+        <v>0.09174995692863963</v>
       </c>
       <c r="T17">
-        <v>0.935593483671798</v>
+        <v>0.9447794776204655</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>28.57578826330967</v>
+        <v>26.78980149685281</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08350836382005729</v>
+        <v>0.08337301596092493</v>
       </c>
       <c r="C18">
-        <v>92.35336477989881</v>
+        <v>91.31731027344667</v>
       </c>
       <c r="D18">
-        <v>103.9447387203954</v>
+        <v>104.0043950852243</v>
       </c>
       <c r="E18">
-        <v>-7.43971318760714</v>
+        <v>-6.344002316326101</v>
       </c>
       <c r="F18">
-        <v>17.5313739404966</v>
+        <v>18.62708481177764</v>
       </c>
       <c r="G18">
         <v>5.94</v>
@@ -2751,28 +2751,28 @@
         <v>23.624</v>
       </c>
       <c r="M18">
-        <v>0.8818281092069787</v>
+        <v>0.936942366032415</v>
       </c>
       <c r="N18">
-        <v>22.74217189079302</v>
+        <v>22.68705763396759</v>
       </c>
       <c r="O18">
-        <v>4.548434378158605</v>
+        <v>4.537411526793518</v>
       </c>
       <c r="P18">
-        <v>18.19373751263442</v>
+        <v>18.14964610717407</v>
       </c>
       <c r="Q18">
-        <v>24.12373751263442</v>
+        <v>24.07964610717407</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09174995692863963</v>
+        <v>0.09220748910954812</v>
       </c>
       <c r="T18">
-        <v>0.9447794776204655</v>
+        <v>0.9541868208209083</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>26.78980149685281</v>
+        <v>25.21393082056735</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08337301596092493</v>
+        <v>0.08323766810179259</v>
       </c>
       <c r="C19">
-        <v>91.31731027344667</v>
+        <v>90.28132428273871</v>
       </c>
       <c r="D19">
-        <v>104.0043950852243</v>
+        <v>104.0641199657974</v>
       </c>
       <c r="E19">
-        <v>-6.344002316326101</v>
+        <v>-5.248291445045062</v>
       </c>
       <c r="F19">
-        <v>18.62708481177764</v>
+        <v>19.72279568305867</v>
       </c>
       <c r="G19">
         <v>5.94</v>
@@ -2833,28 +2833,28 @@
         <v>23.624</v>
       </c>
       <c r="M19">
-        <v>0.936942366032415</v>
+        <v>0.9920566228578512</v>
       </c>
       <c r="N19">
-        <v>22.68705763396759</v>
+        <v>22.63194337714215</v>
       </c>
       <c r="O19">
-        <v>4.537411526793518</v>
+        <v>4.52638867542843</v>
       </c>
       <c r="P19">
-        <v>18.14964610717407</v>
+        <v>18.10555470171372</v>
       </c>
       <c r="Q19">
-        <v>24.07964610717407</v>
+        <v>24.03555470171372</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09220748910954812</v>
+        <v>0.09267618061194219</v>
       </c>
       <c r="T19">
-        <v>0.9541868208209083</v>
+        <v>0.963823611416484</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>25.21393082056735</v>
+        <v>23.81315688609138</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0832376681017926</v>
+        <v>0.08310232024266026</v>
       </c>
       <c r="C20">
-        <v>90.28132428273869</v>
+        <v>89.245406925879</v>
       </c>
       <c r="D20">
-        <v>104.0641199657974</v>
+        <v>104.1239134802187</v>
       </c>
       <c r="E20">
-        <v>-5.248291445045066</v>
+        <v>-4.152580573764027</v>
       </c>
       <c r="F20">
-        <v>19.72279568305867</v>
+        <v>20.81850655433971</v>
       </c>
       <c r="G20">
         <v>5.94</v>
@@ -2915,28 +2915,28 @@
         <v>23.624</v>
       </c>
       <c r="M20">
-        <v>0.9920566228578511</v>
+        <v>1.047170879683287</v>
       </c>
       <c r="N20">
-        <v>22.63194337714215</v>
+        <v>22.57682912031672</v>
       </c>
       <c r="O20">
-        <v>4.52638867542843</v>
+        <v>4.515365824063344</v>
       </c>
       <c r="P20">
-        <v>18.10555470171372</v>
+        <v>18.06146329625337</v>
       </c>
       <c r="Q20">
-        <v>24.03555470171372</v>
+        <v>23.99146329625337</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09267618061194219</v>
+        <v>0.093156444744025</v>
       </c>
       <c r="T20">
-        <v>0.9638236114164839</v>
+        <v>0.9736983474588639</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>23.81315688609138</v>
+        <v>22.559832839455</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08310232024266026</v>
+        <v>0.08296697238352789</v>
       </c>
       <c r="C21">
-        <v>89.245406925879</v>
+        <v>88.20955832124311</v>
       </c>
       <c r="D21">
-        <v>104.1239134802187</v>
+        <v>104.1837757468639</v>
       </c>
       <c r="E21">
-        <v>-4.152580573764027</v>
+        <v>-3.056869702482988</v>
       </c>
       <c r="F21">
-        <v>20.81850655433971</v>
+        <v>21.91421742562075</v>
       </c>
       <c r="G21">
         <v>5.94</v>
@@ -2997,28 +2997,28 @@
         <v>23.624</v>
       </c>
       <c r="M21">
-        <v>1.047170879683287</v>
+        <v>1.102285136508724</v>
       </c>
       <c r="N21">
-        <v>22.57682912031672</v>
+        <v>22.52171486349128</v>
       </c>
       <c r="O21">
-        <v>4.515365824063344</v>
+        <v>4.504342972698256</v>
       </c>
       <c r="P21">
-        <v>18.06146329625337</v>
+        <v>18.01737189079302</v>
       </c>
       <c r="Q21">
-        <v>23.99146329625337</v>
+        <v>23.94737189079302</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.093156444744025</v>
+        <v>0.09364871547940987</v>
       </c>
       <c r="T21">
-        <v>0.9736983474588639</v>
+        <v>0.983819951902303</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>22.559832839455</v>
+        <v>21.43184119748225</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08296697238352789</v>
+        <v>0.08283162452439555</v>
       </c>
       <c r="C22">
-        <v>88.20955832124311</v>
+        <v>87.17377858747909</v>
       </c>
       <c r="D22">
-        <v>104.1837757468639</v>
+        <v>104.2437068843809</v>
       </c>
       <c r="E22">
-        <v>-3.056869702482988</v>
+        <v>-1.961158831201953</v>
       </c>
       <c r="F22">
-        <v>21.91421742562075</v>
+        <v>23.00992829690178</v>
       </c>
       <c r="G22">
         <v>5.94</v>
@@ -3079,28 +3079,28 @@
         <v>23.624</v>
       </c>
       <c r="M22">
-        <v>1.102285136508724</v>
+        <v>1.15739939333416</v>
       </c>
       <c r="N22">
-        <v>22.52171486349128</v>
+        <v>22.46660060666584</v>
       </c>
       <c r="O22">
-        <v>4.504342972698256</v>
+        <v>4.493320121333169</v>
       </c>
       <c r="P22">
-        <v>18.01737189079302</v>
+        <v>17.97328048533267</v>
       </c>
       <c r="Q22">
-        <v>23.94737189079302</v>
+        <v>23.90328048533267</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09364871547940987</v>
+        <v>0.09415344876505766</v>
       </c>
       <c r="T22">
-        <v>0.983819951902303</v>
+        <v>0.9941977994962092</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>21.43184119748225</v>
+        <v>20.41127733093547</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08283162452439555</v>
+        <v>0.08269627666526319</v>
       </c>
       <c r="C23">
-        <v>87.17377858747909</v>
+        <v>86.13806784350811</v>
       </c>
       <c r="D23">
-        <v>104.2437068843809</v>
+        <v>104.3037070116909</v>
       </c>
       <c r="E23">
-        <v>-1.961158831201953</v>
+        <v>-0.8654479599209175</v>
       </c>
       <c r="F23">
-        <v>23.00992829690178</v>
+        <v>24.10563916818282</v>
       </c>
       <c r="G23">
         <v>5.94</v>
@@ -3161,28 +3161,28 @@
         <v>23.624</v>
       </c>
       <c r="M23">
-        <v>1.15739939333416</v>
+        <v>1.212513650159596</v>
       </c>
       <c r="N23">
-        <v>22.46660060666584</v>
+        <v>22.41148634984041</v>
       </c>
       <c r="O23">
-        <v>4.493320121333169</v>
+        <v>4.482297269968082</v>
       </c>
       <c r="P23">
-        <v>17.97328048533267</v>
+        <v>17.92918907987232</v>
       </c>
       <c r="Q23">
-        <v>23.90328048533267</v>
+        <v>23.85918907987232</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09415344876505766</v>
+        <v>0.0946711239298246</v>
       </c>
       <c r="T23">
-        <v>0.9941977994962092</v>
+        <v>1.004841745746369</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>20.41127733093547</v>
+        <v>19.48349199771113</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08269627666526319</v>
+        <v>0.08256092880613085</v>
       </c>
       <c r="C24">
-        <v>86.13806784350811</v>
+        <v>85.10242620852524</v>
       </c>
       <c r="D24">
-        <v>104.3037070116909</v>
+        <v>104.3637762479891</v>
       </c>
       <c r="E24">
-        <v>-0.8654479599209175</v>
+        <v>0.2302629113601213</v>
       </c>
       <c r="F24">
-        <v>24.10563916818282</v>
+        <v>25.20135003946386</v>
       </c>
       <c r="G24">
         <v>5.94</v>
@@ -3243,28 +3243,28 @@
         <v>23.624</v>
       </c>
       <c r="M24">
-        <v>1.212513650159596</v>
+        <v>1.267627906985032</v>
       </c>
       <c r="N24">
-        <v>22.41148634984041</v>
+        <v>22.35637209301497</v>
       </c>
       <c r="O24">
-        <v>4.482297269968082</v>
+        <v>4.471274418602994</v>
       </c>
       <c r="P24">
-        <v>17.92918907987232</v>
+        <v>17.88509767441197</v>
       </c>
       <c r="Q24">
-        <v>23.85918907987232</v>
+        <v>23.81509767441197</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0946711239298246</v>
+        <v>0.09520224520276734</v>
       </c>
       <c r="T24">
-        <v>1.004841745746369</v>
+        <v>1.015762158132897</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>19.48349199771113</v>
+        <v>18.63638364998456</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08256092880613085</v>
+        <v>0.08242558094699851</v>
       </c>
       <c r="C25">
-        <v>85.10242620852524</v>
+        <v>84.0668538020004</v>
       </c>
       <c r="D25">
-        <v>104.3637762479891</v>
+        <v>104.4239147127453</v>
       </c>
       <c r="E25">
-        <v>0.2302629113601213</v>
+        <v>1.32597378264116</v>
       </c>
       <c r="F25">
-        <v>25.20135003946386</v>
+        <v>26.2970609107449</v>
       </c>
       <c r="G25">
         <v>5.94</v>
@@ -3325,28 +3325,28 @@
         <v>23.624</v>
       </c>
       <c r="M25">
-        <v>1.267627906985032</v>
+        <v>1.322742163810468</v>
       </c>
       <c r="N25">
-        <v>22.35637209301497</v>
+        <v>22.30125783618954</v>
       </c>
       <c r="O25">
-        <v>4.471274418602994</v>
+        <v>4.460251567237907</v>
       </c>
       <c r="P25">
-        <v>17.88509767441197</v>
+        <v>17.84100626895163</v>
       </c>
       <c r="Q25">
-        <v>23.81509767441197</v>
+        <v>23.77100626895163</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09520224520276734</v>
+        <v>0.09574734335131382</v>
       </c>
       <c r="T25">
-        <v>1.015762158132897</v>
+        <v>1.026969949792755</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>18.63638364998456</v>
+        <v>17.85986766456854</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08242558094699849</v>
+        <v>0.08229023308786614</v>
       </c>
       <c r="C26">
-        <v>84.0668538020004</v>
+        <v>83.03135074367891</v>
       </c>
       <c r="D26">
-        <v>104.4239147127453</v>
+        <v>104.4841225257048</v>
       </c>
       <c r="E26">
-        <v>1.325973782641157</v>
+        <v>2.421684653922195</v>
       </c>
       <c r="F26">
-        <v>26.29706091074489</v>
+        <v>27.39277178202593</v>
       </c>
       <c r="G26">
         <v>5.94</v>
@@ -3407,28 +3407,28 @@
         <v>23.624</v>
       </c>
       <c r="M26">
-        <v>1.322742163810468</v>
+        <v>1.377856420635904</v>
       </c>
       <c r="N26">
-        <v>22.30125783618954</v>
+        <v>22.2461435793641</v>
       </c>
       <c r="O26">
-        <v>4.460251567237907</v>
+        <v>4.449228715872819</v>
       </c>
       <c r="P26">
-        <v>17.84100626895163</v>
+        <v>17.79691486349128</v>
       </c>
       <c r="Q26">
-        <v>23.77100626895163</v>
+        <v>23.72691486349128</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0957473433513138</v>
+        <v>0.09630697745048819</v>
       </c>
       <c r="T26">
-        <v>1.026969949792755</v>
+        <v>1.038476615896875</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>17.85986766456854</v>
+        <v>17.1454729579858</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08229023308786614</v>
+        <v>0.08215488522873379</v>
       </c>
       <c r="C27">
-        <v>83.03135074367891</v>
+        <v>81.99591715358252</v>
       </c>
       <c r="D27">
-        <v>104.4841225257048</v>
+        <v>104.5443998068895</v>
       </c>
       <c r="E27">
-        <v>2.421684653922195</v>
+        <v>3.517395525203234</v>
       </c>
       <c r="F27">
-        <v>27.39277178202593</v>
+        <v>28.48848265330697</v>
       </c>
       <c r="G27">
         <v>5.94</v>
@@ -3489,28 +3489,28 @@
         <v>23.624</v>
       </c>
       <c r="M27">
-        <v>1.377856420635904</v>
+        <v>1.432970677461341</v>
       </c>
       <c r="N27">
-        <v>22.2461435793641</v>
+        <v>22.19102932253866</v>
       </c>
       <c r="O27">
-        <v>4.449228715872819</v>
+        <v>4.438205864507732</v>
       </c>
       <c r="P27">
-        <v>17.79691486349128</v>
+        <v>17.75282345803093</v>
       </c>
       <c r="Q27">
-        <v>23.72691486349128</v>
+        <v>23.68282345803093</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09630697745048819</v>
+        <v>0.0968817367955862</v>
       </c>
       <c r="T27">
-        <v>1.038476615896875</v>
+        <v>1.050294272976783</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>17.1454729579858</v>
+        <v>16.48603169037096</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08215488522873379</v>
+        <v>0.08201953736960146</v>
       </c>
       <c r="C28">
-        <v>81.99591715358252</v>
+        <v>80.96055315201005</v>
       </c>
       <c r="D28">
-        <v>104.5443998068895</v>
+        <v>104.6047466765981</v>
       </c>
       <c r="E28">
-        <v>3.517395525203234</v>
+        <v>4.613106396484273</v>
       </c>
       <c r="F28">
-        <v>28.48848265330697</v>
+        <v>29.58419352458801</v>
       </c>
       <c r="G28">
         <v>5.94</v>
@@ -3571,28 +3571,28 @@
         <v>23.624</v>
       </c>
       <c r="M28">
-        <v>1.432970677461341</v>
+        <v>1.488084934286777</v>
       </c>
       <c r="N28">
-        <v>22.19102932253866</v>
+        <v>22.13591506571322</v>
       </c>
       <c r="O28">
-        <v>4.438205864507732</v>
+        <v>4.427183013142645</v>
       </c>
       <c r="P28">
-        <v>17.75282345803093</v>
+        <v>17.70873205257058</v>
       </c>
       <c r="Q28">
-        <v>23.68282345803093</v>
+        <v>23.63873205257058</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0968817367955862</v>
+        <v>0.09747224297205678</v>
       </c>
       <c r="T28">
-        <v>1.050294272976783</v>
+        <v>1.062435701483537</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>16.48603169037096</v>
+        <v>15.87543792406092</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08201953736960146</v>
+        <v>0.08188418951046909</v>
       </c>
       <c r="C29">
-        <v>80.96055315201005</v>
+        <v>79.9252588595383</v>
       </c>
       <c r="D29">
-        <v>104.6047466765981</v>
+        <v>104.6651632554074</v>
       </c>
       <c r="E29">
-        <v>4.613106396484273</v>
+        <v>5.708817267765312</v>
       </c>
       <c r="F29">
-        <v>29.58419352458801</v>
+        <v>30.67990439586905</v>
       </c>
       <c r="G29">
         <v>5.94</v>
@@ -3653,28 +3653,28 @@
         <v>23.624</v>
       </c>
       <c r="M29">
-        <v>1.488084934286777</v>
+        <v>1.543199191112213</v>
       </c>
       <c r="N29">
-        <v>22.13591506571322</v>
+        <v>22.08080080888779</v>
       </c>
       <c r="O29">
-        <v>4.427183013142645</v>
+        <v>4.416160161777558</v>
       </c>
       <c r="P29">
-        <v>17.70873205257058</v>
+        <v>17.66464064711023</v>
       </c>
       <c r="Q29">
-        <v>23.63873205257058</v>
+        <v>23.59464064711023</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09747224297205678</v>
+        <v>0.09807915209787374</v>
       </c>
       <c r="T29">
-        <v>1.062435701483537</v>
+        <v>1.074914391893257</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>15.87543792406092</v>
+        <v>15.3084579982016</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08188418951046909</v>
+        <v>0.08174884165133675</v>
       </c>
       <c r="C30">
-        <v>79.9252588595383</v>
+        <v>78.89003439702272</v>
       </c>
       <c r="D30">
-        <v>104.6651632554074</v>
+        <v>104.7256496641728</v>
       </c>
       <c r="E30">
-        <v>5.708817267765312</v>
+        <v>6.804528139046347</v>
       </c>
       <c r="F30">
-        <v>30.67990439586905</v>
+        <v>31.77561526715008</v>
       </c>
       <c r="G30">
         <v>5.94</v>
@@ -3735,28 +3735,28 @@
         <v>23.624</v>
       </c>
       <c r="M30">
-        <v>1.543199191112213</v>
+        <v>1.598313447937649</v>
       </c>
       <c r="N30">
-        <v>22.08080080888779</v>
+        <v>22.02568655206235</v>
       </c>
       <c r="O30">
-        <v>4.416160161777558</v>
+        <v>4.405137310412471</v>
       </c>
       <c r="P30">
-        <v>17.66464064711023</v>
+        <v>17.62054924164988</v>
       </c>
       <c r="Q30">
-        <v>23.59464064711023</v>
+        <v>23.55054924164988</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09807915209787374</v>
+        <v>0.09870315725540388</v>
       </c>
       <c r="T30">
-        <v>1.074914391893257</v>
+        <v>1.087744594708884</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>15.3084579982016</v>
+        <v>14.78058013619465</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08174884165133675</v>
+        <v>0.08161349379220439</v>
       </c>
       <c r="C31">
-        <v>78.89003439702273</v>
+        <v>77.85487988559838</v>
       </c>
       <c r="D31">
-        <v>104.7256496641728</v>
+        <v>104.7862060240295</v>
       </c>
       <c r="E31">
-        <v>6.804528139046344</v>
+        <v>7.900239010327379</v>
       </c>
       <c r="F31">
-        <v>31.77561526715008</v>
+        <v>32.87132613843112</v>
       </c>
       <c r="G31">
         <v>5.94</v>
@@ -3817,28 +3817,28 @@
         <v>23.624</v>
       </c>
       <c r="M31">
-        <v>1.598313447937649</v>
+        <v>1.653427704763085</v>
       </c>
       <c r="N31">
-        <v>22.02568655206235</v>
+        <v>21.97057229523692</v>
       </c>
       <c r="O31">
-        <v>4.405137310412471</v>
+        <v>4.394114459047383</v>
       </c>
       <c r="P31">
-        <v>17.62054924164988</v>
+        <v>17.57645783618953</v>
       </c>
       <c r="Q31">
-        <v>23.55054924164988</v>
+        <v>23.50645783618953</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09870315725540388</v>
+        <v>0.09934499113172057</v>
       </c>
       <c r="T31">
-        <v>1.087744594708884</v>
+        <v>1.100941374747815</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>14.78058013619465</v>
+        <v>14.28789413165483</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08161349379220439</v>
+        <v>0.08147814593307204</v>
       </c>
       <c r="C32">
-        <v>77.85487988559838</v>
+        <v>76.81979544668057</v>
       </c>
       <c r="D32">
-        <v>104.7862060240295</v>
+        <v>104.8468324563927</v>
       </c>
       <c r="E32">
-        <v>7.900239010327379</v>
+        <v>8.995949881608421</v>
       </c>
       <c r="F32">
-        <v>32.87132613843112</v>
+        <v>33.96703700971216</v>
       </c>
       <c r="G32">
         <v>5.94</v>
@@ -3899,28 +3899,28 @@
         <v>23.624</v>
       </c>
       <c r="M32">
-        <v>1.653427704763085</v>
+        <v>1.708541961588521</v>
       </c>
       <c r="N32">
-        <v>21.97057229523692</v>
+        <v>21.91545803841148</v>
       </c>
       <c r="O32">
-        <v>4.394114459047383</v>
+        <v>4.383091607682296</v>
       </c>
       <c r="P32">
-        <v>17.57645783618953</v>
+        <v>17.53236643072918</v>
       </c>
       <c r="Q32">
-        <v>23.50645783618953</v>
+        <v>23.46236643072918</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09934499113172057</v>
+        <v>0.1000054288885102</v>
       </c>
       <c r="T32">
-        <v>1.100941374747815</v>
+        <v>1.114520670150194</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>14.28789413165483</v>
+        <v>13.82699432095629</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08147814593307204</v>
+        <v>0.08134279807393968</v>
       </c>
       <c r="C33">
-        <v>76.81979544668057</v>
+        <v>75.78478120196587</v>
       </c>
       <c r="D33">
-        <v>104.8468324563927</v>
+        <v>104.9075290829591</v>
       </c>
       <c r="E33">
-        <v>8.995949881608421</v>
+        <v>10.09166075288946</v>
       </c>
       <c r="F33">
-        <v>33.96703700971216</v>
+        <v>35.06274788099319</v>
       </c>
       <c r="G33">
         <v>5.94</v>
@@ -3981,28 +3981,28 @@
         <v>23.624</v>
       </c>
       <c r="M33">
-        <v>1.708541961588521</v>
+        <v>1.763656218413957</v>
       </c>
       <c r="N33">
-        <v>21.91545803841148</v>
+        <v>21.86034378158605</v>
       </c>
       <c r="O33">
-        <v>4.383091607682296</v>
+        <v>4.372068756317209</v>
       </c>
       <c r="P33">
-        <v>17.53236643072918</v>
+        <v>17.48827502526884</v>
       </c>
       <c r="Q33">
-        <v>23.46236643072918</v>
+        <v>23.41827502526884</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1000054288885102</v>
+        <v>0.1006852912852054</v>
       </c>
       <c r="T33">
-        <v>1.114520670150194</v>
+        <v>1.128499356593818</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>13.82699432095629</v>
+        <v>13.39490074842641</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08134279807393968</v>
+        <v>0.08120745021480735</v>
       </c>
       <c r="C34">
-        <v>75.78478120196587</v>
+        <v>74.74983727343272</v>
       </c>
       <c r="D34">
-        <v>104.9075290829591</v>
+        <v>104.9682960257069</v>
       </c>
       <c r="E34">
-        <v>10.09166075288946</v>
+        <v>11.18737162417049</v>
       </c>
       <c r="F34">
-        <v>35.06274788099319</v>
+        <v>36.15845875227423</v>
       </c>
       <c r="G34">
         <v>5.94</v>
@@ -4063,28 +4063,28 @@
         <v>23.624</v>
       </c>
       <c r="M34">
-        <v>1.763656218413957</v>
+        <v>1.818770475239394</v>
       </c>
       <c r="N34">
-        <v>21.86034378158605</v>
+        <v>21.80522952476061</v>
       </c>
       <c r="O34">
-        <v>4.372068756317209</v>
+        <v>4.361045904952122</v>
       </c>
       <c r="P34">
-        <v>17.48827502526884</v>
+        <v>17.44418361980849</v>
       </c>
       <c r="Q34">
-        <v>23.41827502526884</v>
+        <v>23.37418361980849</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1006852912852054</v>
+        <v>0.101385448081802</v>
       </c>
       <c r="T34">
-        <v>1.128499356593818</v>
+        <v>1.142895317259641</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>13.39490074842641</v>
+        <v>12.98899466514076</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08120745021480735</v>
+        <v>0.081480102355675</v>
       </c>
       <c r="C35">
-        <v>74.74983727343272</v>
+        <v>73.53178599181548</v>
       </c>
       <c r="D35">
-        <v>104.9682960257069</v>
+        <v>104.8459556153708</v>
       </c>
       <c r="E35">
-        <v>11.18737162417049</v>
+        <v>12.28308249545153</v>
       </c>
       <c r="F35">
-        <v>36.15845875227423</v>
+        <v>37.25416962355527</v>
       </c>
       <c r="G35">
         <v>5.94</v>
@@ -4145,45 +4145,45 @@
         <v>23.624</v>
       </c>
       <c r="M35">
-        <v>1.818770475239394</v>
+        <v>1.929765986500163</v>
       </c>
       <c r="N35">
-        <v>21.80522952476061</v>
+        <v>21.69423401349984</v>
       </c>
       <c r="O35">
-        <v>4.361045904952122</v>
+        <v>4.338846802699968</v>
       </c>
       <c r="P35">
-        <v>17.44418361980849</v>
+        <v>17.35538721079987</v>
       </c>
       <c r="Q35">
-        <v>23.37418361980849</v>
+        <v>23.28538721079987</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.101385448081802</v>
+        <v>0.1021068217510227</v>
       </c>
       <c r="T35">
-        <v>1.142895317259641</v>
+        <v>1.157727519157761</v>
       </c>
       <c r="U35">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y35">
-        <v>12.98899466514076</v>
+        <v>12.24189884434882</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.081480102355675</v>
+        <v>0.08135675449654264</v>
       </c>
       <c r="C36">
-        <v>73.53178599181548</v>
+        <v>72.49138659343865</v>
       </c>
       <c r="D36">
-        <v>104.8459556153708</v>
+        <v>104.9012670882749</v>
       </c>
       <c r="E36">
-        <v>12.28308249545153</v>
+        <v>13.37879336673257</v>
       </c>
       <c r="F36">
-        <v>37.25416962355527</v>
+        <v>38.34988049483631</v>
       </c>
       <c r="G36">
         <v>5.94</v>
@@ -4227,28 +4227,28 @@
         <v>23.624</v>
       </c>
       <c r="M36">
-        <v>1.929765986500163</v>
+        <v>1.986523809632521</v>
       </c>
       <c r="N36">
-        <v>21.69423401349984</v>
+        <v>21.63747619036748</v>
       </c>
       <c r="O36">
-        <v>4.338846802699968</v>
+        <v>4.327495238073497</v>
       </c>
       <c r="P36">
-        <v>17.35538721079987</v>
+        <v>17.30998095229399</v>
       </c>
       <c r="Q36">
-        <v>23.28538721079987</v>
+        <v>23.23998095229399</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1021068217510227</v>
+        <v>0.1028503915331425</v>
       </c>
       <c r="T36">
-        <v>1.157727519157761</v>
+        <v>1.1730160964989</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>12.24189884434882</v>
+        <v>11.89213030593885</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08135675449654264</v>
+        <v>0.08123340663741029</v>
       </c>
       <c r="C37">
-        <v>72.49138659343865</v>
+        <v>71.45104558498886</v>
       </c>
       <c r="D37">
-        <v>104.9012670882749</v>
+        <v>104.9566369511062</v>
       </c>
       <c r="E37">
-        <v>13.37879336673257</v>
+        <v>14.47450423801361</v>
       </c>
       <c r="F37">
-        <v>38.34988049483631</v>
+        <v>39.44559136611735</v>
       </c>
       <c r="G37">
         <v>5.94</v>
@@ -4309,28 +4309,28 @@
         <v>23.624</v>
       </c>
       <c r="M37">
-        <v>1.986523809632521</v>
+        <v>2.043281632764879</v>
       </c>
       <c r="N37">
-        <v>21.63747619036748</v>
+        <v>21.58071836723513</v>
       </c>
       <c r="O37">
-        <v>4.327495238073497</v>
+        <v>4.316143673447026</v>
       </c>
       <c r="P37">
-        <v>17.30998095229399</v>
+        <v>17.2645746937881</v>
       </c>
       <c r="Q37">
-        <v>23.23998095229399</v>
+        <v>23.1945746937881</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1028503915331425</v>
+        <v>0.1036171978709536</v>
       </c>
       <c r="T37">
-        <v>1.1730160964989</v>
+        <v>1.18878244188195</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.89213030593885</v>
+        <v>11.5617933529961</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08123340663741029</v>
+        <v>0.08111005877827795</v>
       </c>
       <c r="C38">
-        <v>71.45104558498886</v>
+        <v>70.41076305897454</v>
       </c>
       <c r="D38">
-        <v>104.9566369511062</v>
+        <v>105.0120652963729</v>
       </c>
       <c r="E38">
-        <v>14.4745042380136</v>
+        <v>15.57021510929464</v>
       </c>
       <c r="F38">
-        <v>39.44559136611734</v>
+        <v>40.54130223739838</v>
       </c>
       <c r="G38">
         <v>5.94</v>
@@ -4391,28 +4391,28 @@
         <v>23.624</v>
       </c>
       <c r="M38">
-        <v>2.043281632764878</v>
+        <v>2.100039455897236</v>
       </c>
       <c r="N38">
-        <v>21.58071836723513</v>
+        <v>21.52396054410277</v>
       </c>
       <c r="O38">
-        <v>4.316143673447026</v>
+        <v>4.304792108820553</v>
       </c>
       <c r="P38">
-        <v>17.2645746937881</v>
+        <v>17.21916843528221</v>
       </c>
       <c r="Q38">
-        <v>23.1945746937881</v>
+        <v>23.14916843528221</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1036171978709536</v>
+        <v>0.1044083472671078</v>
       </c>
       <c r="T38">
-        <v>1.188782441881949</v>
+        <v>1.205049306166049</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>11.56179335299611</v>
+        <v>11.24931245156378</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08111005877827795</v>
+        <v>0.0809867109191456</v>
       </c>
       <c r="C39">
-        <v>70.41076305897454</v>
+        <v>69.37053910809965</v>
       </c>
       <c r="D39">
-        <v>105.0120652963729</v>
+        <v>105.0675522167791</v>
       </c>
       <c r="E39">
-        <v>15.57021510929464</v>
+        <v>16.66592598057568</v>
       </c>
       <c r="F39">
-        <v>40.54130223739838</v>
+        <v>41.63701310867942</v>
       </c>
       <c r="G39">
         <v>5.94</v>
@@ -4473,28 +4473,28 @@
         <v>23.624</v>
       </c>
       <c r="M39">
-        <v>2.100039455897236</v>
+        <v>2.156797279029594</v>
       </c>
       <c r="N39">
-        <v>21.52396054410277</v>
+        <v>21.46720272097041</v>
       </c>
       <c r="O39">
-        <v>4.304792108820553</v>
+        <v>4.293440544194082</v>
       </c>
       <c r="P39">
-        <v>17.21916843528221</v>
+        <v>17.17376217677633</v>
       </c>
       <c r="Q39">
-        <v>23.14916843528221</v>
+        <v>23.10376217677633</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1044083472671078</v>
+        <v>0.1052250176115252</v>
       </c>
       <c r="T39">
-        <v>1.205049306166049</v>
+        <v>1.221840908007699</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>11.24931245156378</v>
+        <v>10.95327791336473</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0809867109191456</v>
+        <v>0.08086336306001325</v>
       </c>
       <c r="C40">
-        <v>69.37053910809965</v>
+        <v>68.3303738252641</v>
       </c>
       <c r="D40">
-        <v>105.0675522167791</v>
+        <v>105.1230978052246</v>
       </c>
       <c r="E40">
-        <v>16.66592598057568</v>
+        <v>17.76163685185672</v>
       </c>
       <c r="F40">
-        <v>41.63701310867942</v>
+        <v>42.73272397996045</v>
       </c>
       <c r="G40">
         <v>5.94</v>
@@ -4555,28 +4555,28 @@
         <v>23.624</v>
       </c>
       <c r="M40">
-        <v>2.156797279029594</v>
+        <v>2.213555102161951</v>
       </c>
       <c r="N40">
-        <v>21.46720272097041</v>
+        <v>21.41044489783805</v>
       </c>
       <c r="O40">
-        <v>4.293440544194082</v>
+        <v>4.28208897956761</v>
       </c>
       <c r="P40">
-        <v>17.17376217677633</v>
+        <v>17.12835591827044</v>
       </c>
       <c r="Q40">
-        <v>23.10376217677633</v>
+        <v>23.05835591827044</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1052250176115252</v>
+        <v>0.1060684640328086</v>
       </c>
       <c r="T40">
-        <v>1.221840908007699</v>
+        <v>1.239183054172027</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.95327791336473</v>
+        <v>10.67242463353487</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08086336306001325</v>
+        <v>0.08074001520088091</v>
       </c>
       <c r="C41">
-        <v>68.3303738252641</v>
+        <v>67.29026730356445</v>
       </c>
       <c r="D41">
-        <v>105.1230978052246</v>
+        <v>105.1787021548059</v>
       </c>
       <c r="E41">
-        <v>17.76163685185672</v>
+        <v>18.85734772313776</v>
       </c>
       <c r="F41">
-        <v>42.73272397996045</v>
+        <v>43.8284348512415</v>
       </c>
       <c r="G41">
         <v>5.94</v>
@@ -4637,28 +4637,28 @@
         <v>23.624</v>
       </c>
       <c r="M41">
-        <v>2.213555102161951</v>
+        <v>2.270312925294309</v>
       </c>
       <c r="N41">
-        <v>21.41044489783805</v>
+        <v>21.35368707470569</v>
       </c>
       <c r="O41">
-        <v>4.28208897956761</v>
+        <v>4.270737414941139</v>
       </c>
       <c r="P41">
-        <v>17.12835591827044</v>
+        <v>17.08294965976456</v>
       </c>
       <c r="Q41">
-        <v>23.05835591827044</v>
+        <v>23.01294965976455</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1060684640328086</v>
+        <v>0.1069400253348015</v>
       </c>
       <c r="T41">
-        <v>1.239183054172027</v>
+        <v>1.257103271875165</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>10.67242463353487</v>
+        <v>10.4056140176965</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08074001520088091</v>
+        <v>0.08061666734174855</v>
       </c>
       <c r="C42">
-        <v>67.29026730356445</v>
+        <v>66.2502196362943</v>
       </c>
       <c r="D42">
-        <v>105.1787021548059</v>
+        <v>105.2343653588168</v>
       </c>
       <c r="E42">
-        <v>18.85734772313776</v>
+        <v>19.9530585944188</v>
       </c>
       <c r="F42">
-        <v>43.8284348512415</v>
+        <v>44.92414572252253</v>
       </c>
       <c r="G42">
         <v>5.94</v>
@@ -4719,28 +4719,28 @@
         <v>23.624</v>
       </c>
       <c r="M42">
-        <v>2.270312925294309</v>
+        <v>2.327070748426667</v>
       </c>
       <c r="N42">
-        <v>21.35368707470569</v>
+        <v>21.29692925157334</v>
       </c>
       <c r="O42">
-        <v>4.270737414941139</v>
+        <v>4.259385850314668</v>
       </c>
       <c r="P42">
-        <v>17.08294965976456</v>
+        <v>17.03754340125867</v>
       </c>
       <c r="Q42">
-        <v>23.01294965976455</v>
+        <v>22.96754340125867</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1069400253348015</v>
+        <v>0.1078411310877094</v>
       </c>
       <c r="T42">
-        <v>1.257103271875165</v>
+        <v>1.27563095458519</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>10.4056140176965</v>
+        <v>10.15181855385024</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08061666734174855</v>
+        <v>0.0804933194826162</v>
       </c>
       <c r="C43">
-        <v>66.2502196362943</v>
+        <v>65.21023091694484</v>
       </c>
       <c r="D43">
-        <v>105.2343653588168</v>
+        <v>105.2900875107484</v>
       </c>
       <c r="E43">
-        <v>19.9530585944188</v>
+        <v>21.04876946569983</v>
       </c>
       <c r="F43">
-        <v>44.92414572252253</v>
+        <v>46.01985659380357</v>
       </c>
       <c r="G43">
         <v>5.94</v>
@@ -4801,28 +4801,28 @@
         <v>23.624</v>
       </c>
       <c r="M43">
-        <v>2.327070748426667</v>
+        <v>2.383828571559025</v>
       </c>
       <c r="N43">
-        <v>21.29692925157334</v>
+        <v>21.24017142844098</v>
       </c>
       <c r="O43">
-        <v>4.259385850314668</v>
+        <v>4.248034285688195</v>
       </c>
       <c r="P43">
-        <v>17.03754340125867</v>
+        <v>16.99213714275278</v>
       </c>
       <c r="Q43">
-        <v>22.96754340125867</v>
+        <v>22.92213714275278</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1078411310877094</v>
+        <v>0.1087733094527866</v>
       </c>
       <c r="T43">
-        <v>1.27563095458519</v>
+        <v>1.294797522905905</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>10.15181855385024</v>
+        <v>9.910108588282377</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0804933194826162</v>
+        <v>0.08095477162348387</v>
       </c>
       <c r="C44">
-        <v>65.21023091694484</v>
+        <v>63.90636191409192</v>
       </c>
       <c r="D44">
-        <v>105.2900875107484</v>
+        <v>105.0819293791765</v>
       </c>
       <c r="E44">
-        <v>21.04876946569983</v>
+        <v>22.14448033698087</v>
       </c>
       <c r="F44">
-        <v>46.01985659380357</v>
+        <v>47.1155674650846</v>
       </c>
       <c r="G44">
         <v>5.94</v>
@@ -4883,45 +4883,45 @@
         <v>23.624</v>
       </c>
       <c r="M44">
-        <v>2.383828571559025</v>
+        <v>2.520682859382026</v>
       </c>
       <c r="N44">
-        <v>21.24017142844098</v>
+        <v>21.10331714061797</v>
       </c>
       <c r="O44">
-        <v>4.248034285688195</v>
+        <v>4.220663428123595</v>
       </c>
       <c r="P44">
-        <v>16.99213714275278</v>
+        <v>16.88265371249438</v>
       </c>
       <c r="Q44">
-        <v>22.92213714275278</v>
+        <v>22.81265371249438</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1087733094527865</v>
+        <v>0.1097381958306734</v>
       </c>
       <c r="T44">
-        <v>1.294797522905905</v>
+        <v>1.314636602395768</v>
       </c>
       <c r="U44">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>9.910108588282377</v>
+        <v>9.372063570818144</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08095477162348387</v>
+        <v>0.0808450237643515</v>
       </c>
       <c r="C45">
-        <v>63.90636191409192</v>
+        <v>62.86008297361722</v>
       </c>
       <c r="D45">
-        <v>105.0819293791765</v>
+        <v>105.1313613099829</v>
       </c>
       <c r="E45">
-        <v>22.14448033698087</v>
+        <v>23.2401912082619</v>
       </c>
       <c r="F45">
-        <v>47.1155674650846</v>
+        <v>48.21127833636564</v>
       </c>
       <c r="G45">
         <v>5.94</v>
@@ -4965,28 +4965,28 @@
         <v>23.624</v>
       </c>
       <c r="M45">
-        <v>2.520682859382026</v>
+        <v>2.579303390995562</v>
       </c>
       <c r="N45">
-        <v>21.10331714061797</v>
+        <v>21.04469660900444</v>
       </c>
       <c r="O45">
-        <v>4.220663428123595</v>
+        <v>4.208939321800888</v>
       </c>
       <c r="P45">
-        <v>16.88265371249438</v>
+        <v>16.83575728720355</v>
       </c>
       <c r="Q45">
-        <v>22.81265371249438</v>
+        <v>22.76575728720355</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1097381958306734</v>
+        <v>0.110737542436342</v>
       </c>
       <c r="T45">
-        <v>1.314636602395768</v>
+        <v>1.33518422043884</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>9.372063570818144</v>
+        <v>9.159062126026823</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0808450237643515</v>
+        <v>0.08073527590521916</v>
       </c>
       <c r="C46">
-        <v>62.86008297361722</v>
+        <v>61.81385056189968</v>
       </c>
       <c r="D46">
-        <v>105.1313613099829</v>
+        <v>105.1808397695464</v>
       </c>
       <c r="E46">
-        <v>23.2401912082619</v>
+        <v>24.33590207954294</v>
       </c>
       <c r="F46">
-        <v>48.21127833636564</v>
+        <v>49.30698920764668</v>
       </c>
       <c r="G46">
         <v>5.94</v>
@@ -5047,28 +5047,28 @@
         <v>23.624</v>
       </c>
       <c r="M46">
-        <v>2.579303390995562</v>
+        <v>2.637923922609097</v>
       </c>
       <c r="N46">
-        <v>21.04469660900444</v>
+        <v>20.9860760773909</v>
       </c>
       <c r="O46">
-        <v>4.208939321800888</v>
+        <v>4.197215215478181</v>
       </c>
       <c r="P46">
-        <v>16.83575728720355</v>
+        <v>16.78886086191272</v>
       </c>
       <c r="Q46">
-        <v>22.76575728720355</v>
+        <v>22.71886086191272</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.110737542436342</v>
+        <v>0.1117732289185803</v>
       </c>
       <c r="T46">
-        <v>1.33518422043884</v>
+        <v>1.356479024592569</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>9.159062126026823</v>
+        <v>8.955527412115114</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08073527590521916</v>
+        <v>0.0806255280460868</v>
       </c>
       <c r="C47">
-        <v>61.81385056189968</v>
+        <v>60.76766474466437</v>
       </c>
       <c r="D47">
-        <v>105.1808397695464</v>
+        <v>105.2303648235921</v>
       </c>
       <c r="E47">
-        <v>24.33590207954294</v>
+        <v>25.43161295082398</v>
       </c>
       <c r="F47">
-        <v>49.30698920764668</v>
+        <v>50.40270007892772</v>
       </c>
       <c r="G47">
         <v>5.94</v>
@@ -5129,28 +5129,28 @@
         <v>23.624</v>
       </c>
       <c r="M47">
-        <v>2.637923922609097</v>
+        <v>2.696544454222633</v>
       </c>
       <c r="N47">
-        <v>20.9860760773909</v>
+        <v>20.92745554577737</v>
       </c>
       <c r="O47">
-        <v>4.197215215478181</v>
+        <v>4.185491109155474</v>
       </c>
       <c r="P47">
-        <v>16.78886086191272</v>
+        <v>16.7419644366219</v>
       </c>
       <c r="Q47">
-        <v>22.71886086191272</v>
+        <v>22.6719644366219</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1117732289185803</v>
+        <v>0.11284727415942</v>
       </c>
       <c r="T47">
-        <v>1.356479024592569</v>
+        <v>1.378562525196437</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.955527412115114</v>
+        <v>8.760842033590874</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0806255280460868</v>
+        <v>0.08051578018695445</v>
       </c>
       <c r="C48">
-        <v>60.76766474466437</v>
+        <v>59.72152558776015</v>
       </c>
       <c r="D48">
-        <v>105.2303648235921</v>
+        <v>105.2799365379689</v>
       </c>
       <c r="E48">
-        <v>25.43161295082398</v>
+        <v>26.52732382210502</v>
       </c>
       <c r="F48">
-        <v>50.40270007892772</v>
+        <v>51.49841095020876</v>
       </c>
       <c r="G48">
         <v>5.94</v>
@@ -5211,28 +5211,28 @@
         <v>23.624</v>
       </c>
       <c r="M48">
-        <v>2.696544454222633</v>
+        <v>2.755164985836168</v>
       </c>
       <c r="N48">
-        <v>20.92745554577737</v>
+        <v>20.86883501416384</v>
       </c>
       <c r="O48">
-        <v>4.185491109155474</v>
+        <v>4.173767002832768</v>
       </c>
       <c r="P48">
-        <v>16.7419644366219</v>
+        <v>16.69506801133107</v>
       </c>
       <c r="Q48">
-        <v>22.6719644366219</v>
+        <v>22.62506801133107</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.11284727415942</v>
+        <v>0.113961849409348</v>
       </c>
       <c r="T48">
-        <v>1.378562525196437</v>
+        <v>1.401479365445734</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.760842033590874</v>
+        <v>8.574441139259154</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08051578018695445</v>
+        <v>0.08040603232782211</v>
       </c>
       <c r="C49">
-        <v>59.72152558776015</v>
+        <v>58.67543315716011</v>
       </c>
       <c r="D49">
-        <v>105.2799365379689</v>
+        <v>105.3295549786499</v>
       </c>
       <c r="E49">
-        <v>26.52732382210502</v>
+        <v>27.62303469338606</v>
       </c>
       <c r="F49">
-        <v>51.49841095020876</v>
+        <v>52.59412182148979</v>
       </c>
       <c r="G49">
         <v>5.94</v>
@@ -5293,28 +5293,28 @@
         <v>23.624</v>
       </c>
       <c r="M49">
-        <v>2.755164985836168</v>
+        <v>2.813785517449704</v>
       </c>
       <c r="N49">
-        <v>20.86883501416384</v>
+        <v>20.8102144825503</v>
       </c>
       <c r="O49">
-        <v>4.173767002832768</v>
+        <v>4.16204289651006</v>
       </c>
       <c r="P49">
-        <v>16.69506801133107</v>
+        <v>16.64817158604024</v>
       </c>
       <c r="Q49">
-        <v>22.62506801133107</v>
+        <v>22.57817158604024</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.113961849409348</v>
+        <v>0.1151192929381194</v>
       </c>
       <c r="T49">
-        <v>1.401479365445734</v>
+        <v>1.425277622627696</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.574441139259154</v>
+        <v>8.395806948857921</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08040603232782211</v>
+        <v>0.08029628446868975</v>
       </c>
       <c r="C50">
-        <v>58.67543315716012</v>
+        <v>57.62938751896174</v>
       </c>
       <c r="D50">
-        <v>105.3295549786499</v>
+        <v>105.3792202117326</v>
       </c>
       <c r="E50">
-        <v>27.62303469338605</v>
+        <v>28.71874556466709</v>
       </c>
       <c r="F50">
-        <v>52.59412182148979</v>
+        <v>53.68983269277083</v>
       </c>
       <c r="G50">
         <v>5.94</v>
@@ -5375,28 +5375,28 @@
         <v>23.624</v>
       </c>
       <c r="M50">
-        <v>2.813785517449703</v>
+        <v>2.872406049063239</v>
       </c>
       <c r="N50">
-        <v>20.8102144825503</v>
+        <v>20.75159395093676</v>
       </c>
       <c r="O50">
-        <v>4.16204289651006</v>
+        <v>4.150318790187352</v>
       </c>
       <c r="P50">
-        <v>16.64817158604024</v>
+        <v>16.60127516074941</v>
       </c>
       <c r="Q50">
-        <v>22.57817158604024</v>
+        <v>22.53127516074941</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1151192929381194</v>
+        <v>0.1163221264091956</v>
       </c>
       <c r="T50">
-        <v>1.425277622627696</v>
+        <v>1.450009144797185</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.395806948857922</v>
+        <v>8.224463949901637</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08029628446868975</v>
+        <v>0.08018653660955741</v>
       </c>
       <c r="C51">
-        <v>57.62938751896174</v>
+        <v>56.58338873938725</v>
       </c>
       <c r="D51">
-        <v>105.3792202117326</v>
+        <v>105.4289323034391</v>
       </c>
       <c r="E51">
-        <v>28.71874556466709</v>
+        <v>29.81445643594813</v>
       </c>
       <c r="F51">
-        <v>53.68983269277083</v>
+        <v>54.78554356405186</v>
       </c>
       <c r="G51">
         <v>5.94</v>
@@ -5457,28 +5457,28 @@
         <v>23.624</v>
       </c>
       <c r="M51">
-        <v>2.872406049063239</v>
+        <v>2.931026580676775</v>
       </c>
       <c r="N51">
-        <v>20.75159395093676</v>
+        <v>20.69297341932323</v>
       </c>
       <c r="O51">
-        <v>4.150318790187352</v>
+        <v>4.138594683864645</v>
       </c>
       <c r="P51">
-        <v>16.60127516074941</v>
+        <v>16.55437873545858</v>
       </c>
       <c r="Q51">
-        <v>22.53127516074941</v>
+        <v>22.48437873545858</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1163221264091956</v>
+        <v>0.1175730732191148</v>
       </c>
       <c r="T51">
-        <v>1.450009144797185</v>
+        <v>1.475729927853455</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>8.224463949901637</v>
+        <v>8.059974670903603</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08018653660955741</v>
+        <v>0.08007678875042505</v>
       </c>
       <c r="C52">
-        <v>56.58338873938725</v>
+        <v>55.53743688478385</v>
       </c>
       <c r="D52">
-        <v>105.4289323034391</v>
+        <v>105.4786913201168</v>
       </c>
       <c r="E52">
-        <v>29.81445643594813</v>
+        <v>30.91016730722916</v>
       </c>
       <c r="F52">
-        <v>54.78554356405186</v>
+        <v>55.8812544353329</v>
       </c>
       <c r="G52">
         <v>5.94</v>
@@ -5539,28 +5539,28 @@
         <v>23.624</v>
       </c>
       <c r="M52">
-        <v>2.931026580676775</v>
+        <v>2.98964711229031</v>
       </c>
       <c r="N52">
-        <v>20.69297341932323</v>
+        <v>20.63435288770969</v>
       </c>
       <c r="O52">
-        <v>4.138594683864645</v>
+        <v>4.126870577541939</v>
       </c>
       <c r="P52">
-        <v>16.55437873545858</v>
+        <v>16.50748231016775</v>
       </c>
       <c r="Q52">
-        <v>22.48437873545858</v>
+        <v>22.43748231016775</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1175730732191148</v>
+        <v>0.1188750790825001</v>
       </c>
       <c r="T52">
-        <v>1.475729927853455</v>
+        <v>1.502500538789572</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>8.059974670903603</v>
+        <v>7.901935951866278</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08007678875042505</v>
+        <v>0.07996704089129271</v>
       </c>
       <c r="C53">
-        <v>55.53743688478385</v>
+        <v>54.49153202162406</v>
       </c>
       <c r="D53">
-        <v>105.4786913201168</v>
+        <v>105.528497328238</v>
       </c>
       <c r="E53">
-        <v>30.91016730722916</v>
+        <v>32.0058781785102</v>
       </c>
       <c r="F53">
-        <v>55.8812544353329</v>
+        <v>56.97696530661394</v>
       </c>
       <c r="G53">
         <v>5.94</v>
@@ -5621,28 +5621,28 @@
         <v>23.624</v>
       </c>
       <c r="M53">
-        <v>2.98964711229031</v>
+        <v>3.048267643903846</v>
       </c>
       <c r="N53">
-        <v>20.63435288770969</v>
+        <v>20.57573235609616</v>
       </c>
       <c r="O53">
-        <v>4.126870577541939</v>
+        <v>4.115146471219232</v>
       </c>
       <c r="P53">
-        <v>16.50748231016775</v>
+        <v>16.46058588487693</v>
       </c>
       <c r="Q53">
-        <v>22.43748231016775</v>
+        <v>22.39058588487693</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1188750790825001</v>
+        <v>0.1202313351901931</v>
       </c>
       <c r="T53">
-        <v>1.502500538789572</v>
+        <v>1.530386591848027</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.901935951866278</v>
+        <v>7.749975645099619</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07996704089129271</v>
+        <v>0.08019649303216035</v>
       </c>
       <c r="C54">
-        <v>54.49153202162406</v>
+        <v>53.2917442662884</v>
       </c>
       <c r="D54">
-        <v>105.528497328238</v>
+        <v>105.4244204441834</v>
       </c>
       <c r="E54">
-        <v>32.0058781785102</v>
+        <v>33.10158904979124</v>
       </c>
       <c r="F54">
-        <v>56.97696530661394</v>
+        <v>58.07267617789498</v>
       </c>
       <c r="G54">
         <v>5.94</v>
@@ -5703,45 +5703,45 @@
         <v>23.624</v>
       </c>
       <c r="M54">
-        <v>3.048267643903846</v>
+        <v>3.153346316459697</v>
       </c>
       <c r="N54">
-        <v>20.57573235609616</v>
+        <v>20.47065368354031</v>
       </c>
       <c r="O54">
-        <v>4.115146471219232</v>
+        <v>4.094130736708061</v>
       </c>
       <c r="P54">
-        <v>16.46058588487693</v>
+        <v>16.37652294683225</v>
       </c>
       <c r="Q54">
-        <v>22.39058588487693</v>
+        <v>22.30652294683225</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1202313351901931</v>
+        <v>0.1216453043237454</v>
       </c>
       <c r="T54">
-        <v>1.530386591848027</v>
+        <v>1.559459285462161</v>
       </c>
       <c r="U54">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V54">
         <v>0.2</v>
       </c>
       <c r="W54">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y54">
-        <v>7.749975645099619</v>
+        <v>7.491723911417054</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08019649303216035</v>
+        <v>0.080093145173028</v>
       </c>
       <c r="C55">
-        <v>53.2917442662884</v>
+        <v>52.24288538947393</v>
       </c>
       <c r="D55">
-        <v>105.4244204441834</v>
+        <v>105.4712724386499</v>
       </c>
       <c r="E55">
-        <v>33.10158904979124</v>
+        <v>34.19729992107229</v>
       </c>
       <c r="F55">
-        <v>58.07267617789498</v>
+        <v>59.16838704917602</v>
       </c>
       <c r="G55">
         <v>5.94</v>
@@ -5785,28 +5785,28 @@
         <v>23.624</v>
       </c>
       <c r="M55">
-        <v>3.153346316459697</v>
+        <v>3.212843416770258</v>
       </c>
       <c r="N55">
-        <v>20.47065368354031</v>
+        <v>20.41115658322974</v>
       </c>
       <c r="O55">
-        <v>4.094130736708061</v>
+        <v>4.082231316645949</v>
       </c>
       <c r="P55">
-        <v>16.37652294683225</v>
+        <v>16.32892526658379</v>
       </c>
       <c r="Q55">
-        <v>22.30652294683225</v>
+        <v>22.25892526658379</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1216453043237454</v>
+        <v>0.1231207503761478</v>
       </c>
       <c r="T55">
-        <v>1.559459285462161</v>
+        <v>1.589796009233432</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.491723911417054</v>
+        <v>7.352988283427848</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.080093145173028</v>
+        <v>0.07998979731389566</v>
       </c>
       <c r="C56">
-        <v>52.24288538947393</v>
+        <v>51.19406817445553</v>
       </c>
       <c r="D56">
-        <v>105.4712724386499</v>
+        <v>105.5181660949126</v>
       </c>
       <c r="E56">
-        <v>34.19729992107229</v>
+        <v>35.29301079235331</v>
       </c>
       <c r="F56">
-        <v>59.16838704917602</v>
+        <v>60.26409792045705</v>
       </c>
       <c r="G56">
         <v>5.94</v>
@@ -5867,28 +5867,28 @@
         <v>23.624</v>
       </c>
       <c r="M56">
-        <v>3.212843416770258</v>
+        <v>3.272340517080818</v>
       </c>
       <c r="N56">
-        <v>20.41115658322974</v>
+        <v>20.35165948291919</v>
       </c>
       <c r="O56">
-        <v>4.082231316645949</v>
+        <v>4.070331896583837</v>
       </c>
       <c r="P56">
-        <v>16.32892526658379</v>
+        <v>16.28132758633535</v>
       </c>
       <c r="Q56">
-        <v>22.25892526658379</v>
+        <v>22.21132758633535</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1231207503761478</v>
+        <v>0.124661771808657</v>
       </c>
       <c r="T56">
-        <v>1.589796009233432</v>
+        <v>1.621481031838981</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>7.352988283427848</v>
+        <v>7.219297587365525</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07998979731389566</v>
+        <v>0.07988644945476331</v>
       </c>
       <c r="C57">
-        <v>51.19406817445553</v>
+        <v>50.1452926768278</v>
       </c>
       <c r="D57">
-        <v>105.5181660949126</v>
+        <v>105.5651014685659</v>
       </c>
       <c r="E57">
-        <v>35.29301079235331</v>
+        <v>36.38872166363436</v>
       </c>
       <c r="F57">
-        <v>60.26409792045705</v>
+        <v>61.3598087917381</v>
       </c>
       <c r="G57">
         <v>5.94</v>
@@ -5949,28 +5949,28 @@
         <v>23.624</v>
       </c>
       <c r="M57">
-        <v>3.272340517080818</v>
+        <v>3.331837617391379</v>
       </c>
       <c r="N57">
-        <v>20.35165948291919</v>
+        <v>20.29216238260862</v>
       </c>
       <c r="O57">
-        <v>4.070331896583837</v>
+        <v>4.058432476521725</v>
       </c>
       <c r="P57">
-        <v>16.28132758633535</v>
+        <v>16.2337299060869</v>
       </c>
       <c r="Q57">
-        <v>22.21132758633535</v>
+        <v>22.1637299060869</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.124661771808657</v>
+        <v>0.1262728396699166</v>
       </c>
       <c r="T57">
-        <v>1.621481031838981</v>
+        <v>1.654606282744783</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>7.219297587365525</v>
+        <v>7.090381559019711</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07988644945476331</v>
+        <v>0.07978310159563096</v>
       </c>
       <c r="C58">
-        <v>50.1452926768278</v>
+        <v>49.09655895228427</v>
       </c>
       <c r="D58">
-        <v>105.5651014685659</v>
+        <v>105.6120786153034</v>
       </c>
       <c r="E58">
-        <v>36.38872166363436</v>
+        <v>37.4844325349154</v>
       </c>
       <c r="F58">
-        <v>61.3598087917381</v>
+        <v>62.45551966301913</v>
       </c>
       <c r="G58">
         <v>5.94</v>
@@ -6031,28 +6031,28 @@
         <v>23.624</v>
       </c>
       <c r="M58">
-        <v>3.331837617391379</v>
+        <v>3.391334717701939</v>
       </c>
       <c r="N58">
-        <v>20.29216238260862</v>
+        <v>20.23266528229806</v>
       </c>
       <c r="O58">
-        <v>4.058432476521725</v>
+        <v>4.046533056459613</v>
       </c>
       <c r="P58">
-        <v>16.2337299060869</v>
+        <v>16.18613222583845</v>
       </c>
       <c r="Q58">
-        <v>22.1637299060869</v>
+        <v>22.11613222583845</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1262728396699166</v>
+        <v>0.127958840920072</v>
       </c>
       <c r="T58">
-        <v>1.654606282744783</v>
+        <v>1.68927224299504</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>7.090381559019711</v>
+        <v>6.965988900089541</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07978310159563096</v>
+        <v>0.0796797537364986</v>
       </c>
       <c r="C59">
-        <v>49.09655895228427</v>
+        <v>48.0478670566176</v>
       </c>
       <c r="D59">
-        <v>105.6120786153034</v>
+        <v>105.6590975909178</v>
       </c>
       <c r="E59">
-        <v>37.4844325349154</v>
+        <v>38.58014340619643</v>
       </c>
       <c r="F59">
-        <v>62.45551966301913</v>
+        <v>63.55123053430017</v>
       </c>
       <c r="G59">
         <v>5.94</v>
@@ -6113,28 +6113,28 @@
         <v>23.624</v>
       </c>
       <c r="M59">
-        <v>3.391334717701939</v>
+        <v>3.450831818012499</v>
       </c>
       <c r="N59">
-        <v>20.23266528229806</v>
+        <v>20.1731681819875</v>
       </c>
       <c r="O59">
-        <v>4.046533056459613</v>
+        <v>4.0346336363975</v>
       </c>
       <c r="P59">
-        <v>16.18613222583845</v>
+        <v>16.13853454559</v>
       </c>
       <c r="Q59">
-        <v>22.11613222583845</v>
+        <v>22.06853454559</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.127958840920072</v>
+        <v>0.1297251279440443</v>
       </c>
       <c r="T59">
-        <v>1.68927224299504</v>
+        <v>1.725588963257215</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.965988900089541</v>
+        <v>6.845885643191445</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0796797537364986</v>
+        <v>0.07957640587736625</v>
       </c>
       <c r="C60">
-        <v>48.0478670566176</v>
+        <v>46.99921704571993</v>
       </c>
       <c r="D60">
-        <v>105.6590975909178</v>
+        <v>105.7061584513011</v>
       </c>
       <c r="E60">
-        <v>38.58014340619643</v>
+        <v>39.67585427747747</v>
       </c>
       <c r="F60">
-        <v>63.55123053430016</v>
+        <v>64.6469414055812</v>
       </c>
       <c r="G60">
         <v>5.94</v>
@@ -6195,28 +6195,28 @@
         <v>23.624</v>
       </c>
       <c r="M60">
-        <v>3.450831818012499</v>
+        <v>3.510328918323059</v>
       </c>
       <c r="N60">
-        <v>20.1731681819875</v>
+        <v>20.11367108167694</v>
       </c>
       <c r="O60">
-        <v>4.0346336363975</v>
+        <v>4.022734216335389</v>
       </c>
       <c r="P60">
-        <v>16.13853454559</v>
+        <v>16.09093686534155</v>
       </c>
       <c r="Q60">
-        <v>22.06853454559</v>
+        <v>22.02093686534155</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1297251279440443</v>
+        <v>0.1315775753106494</v>
       </c>
       <c r="T60">
-        <v>1.725588963257214</v>
+        <v>1.763677230849251</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.845885643191446</v>
+        <v>6.729853683137354</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07957640587736625</v>
+        <v>0.07947305801823393</v>
       </c>
       <c r="C61">
-        <v>46.99921704571993</v>
+        <v>45.95060897558297</v>
       </c>
       <c r="D61">
-        <v>105.7061584513011</v>
+        <v>105.7532612524452</v>
       </c>
       <c r="E61">
-        <v>39.67585427747747</v>
+        <v>40.7715651487585</v>
       </c>
       <c r="F61">
-        <v>64.6469414055812</v>
+        <v>65.74265227686223</v>
       </c>
       <c r="G61">
         <v>5.94</v>
@@ -6277,28 +6277,28 @@
         <v>23.624</v>
       </c>
       <c r="M61">
-        <v>3.510328918323059</v>
+        <v>3.569826018633619</v>
       </c>
       <c r="N61">
-        <v>20.11367108167694</v>
+        <v>20.05417398136638</v>
       </c>
       <c r="O61">
-        <v>4.022734216335389</v>
+        <v>4.010834796273277</v>
       </c>
       <c r="P61">
-        <v>16.09093686534155</v>
+        <v>16.04333918509311</v>
       </c>
       <c r="Q61">
-        <v>22.02093686534155</v>
+        <v>21.97333918509311</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1315775753106494</v>
+        <v>0.1335226450455848</v>
       </c>
       <c r="T61">
-        <v>1.763677230849251</v>
+        <v>1.803669911820889</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.729853683137354</v>
+        <v>6.617689455085065</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07947305801823393</v>
+        <v>0.07936971015910156</v>
       </c>
       <c r="C62">
-        <v>45.95060897558297</v>
+        <v>44.90204290229826</v>
       </c>
       <c r="D62">
-        <v>105.7532612524452</v>
+        <v>105.8004060504415</v>
       </c>
       <c r="E62">
-        <v>40.7715651487585</v>
+        <v>41.86727602003954</v>
       </c>
       <c r="F62">
-        <v>65.74265227686223</v>
+        <v>66.83836314814327</v>
       </c>
       <c r="G62">
         <v>5.94</v>
@@ -6359,28 +6359,28 @@
         <v>23.624</v>
       </c>
       <c r="M62">
-        <v>3.569826018633619</v>
+        <v>3.62932311894418</v>
       </c>
       <c r="N62">
-        <v>20.05417398136638</v>
+        <v>19.99467688105582</v>
       </c>
       <c r="O62">
-        <v>4.010834796273277</v>
+        <v>3.998935376211165</v>
       </c>
       <c r="P62">
-        <v>16.04333918509311</v>
+        <v>15.99574150484466</v>
       </c>
       <c r="Q62">
-        <v>21.97333918509311</v>
+        <v>21.92574150484466</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1335226450455848</v>
+        <v>0.1355674619464143</v>
       </c>
       <c r="T62">
-        <v>1.803669911820889</v>
+        <v>1.845713499509022</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.617689455085065</v>
+        <v>6.509202742706622</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07936971015910156</v>
+        <v>0.07926636229996921</v>
       </c>
       <c r="C63">
-        <v>44.90204290229826</v>
+        <v>43.85351888205747</v>
       </c>
       <c r="D63">
-        <v>105.8004060504415</v>
+        <v>105.8475929014818</v>
       </c>
       <c r="E63">
-        <v>41.86727602003954</v>
+        <v>42.96298689132058</v>
       </c>
       <c r="F63">
-        <v>66.83836314814327</v>
+        <v>67.93407401942432</v>
       </c>
       <c r="G63">
         <v>5.94</v>
@@ -6441,28 +6441,28 @@
         <v>23.624</v>
       </c>
       <c r="M63">
-        <v>3.62932311894418</v>
+        <v>3.68882021925474</v>
       </c>
       <c r="N63">
-        <v>19.99467688105582</v>
+        <v>19.93517978074526</v>
       </c>
       <c r="O63">
-        <v>3.998935376211165</v>
+        <v>3.987035956149052</v>
       </c>
       <c r="P63">
-        <v>15.99574150484466</v>
+        <v>15.94814382459621</v>
       </c>
       <c r="Q63">
-        <v>21.92574150484466</v>
+        <v>21.87814382459621</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1355674619464143</v>
+        <v>0.1377199007893926</v>
       </c>
       <c r="T63">
-        <v>1.845713499509022</v>
+        <v>1.889969907601793</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.509202742706622</v>
+        <v>6.404215601695223</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07926636229996921</v>
+        <v>0.07916301444083686</v>
       </c>
       <c r="C64">
-        <v>43.85351888205747</v>
+        <v>42.8050369711525</v>
       </c>
       <c r="D64">
-        <v>105.8475929014818</v>
+        <v>105.8948218618578</v>
       </c>
       <c r="E64">
-        <v>42.96298689132058</v>
+        <v>44.05869776260161</v>
       </c>
       <c r="F64">
-        <v>67.93407401942432</v>
+        <v>69.02978489070534</v>
       </c>
       <c r="G64">
         <v>5.94</v>
@@ -6523,28 +6523,28 @@
         <v>23.624</v>
       </c>
       <c r="M64">
-        <v>3.68882021925474</v>
+        <v>3.7483173195653</v>
       </c>
       <c r="N64">
-        <v>19.93517978074526</v>
+        <v>19.8756826804347</v>
       </c>
       <c r="O64">
-        <v>3.987035956149052</v>
+        <v>3.975136536086941</v>
       </c>
       <c r="P64">
-        <v>15.94814382459621</v>
+        <v>15.90054614434776</v>
       </c>
       <c r="Q64">
-        <v>21.87814382459621</v>
+        <v>21.83054614434776</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1377199007893926</v>
+        <v>0.1399886876779375</v>
       </c>
       <c r="T64">
-        <v>1.889969907601793</v>
+        <v>1.936618553969849</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.404215601695223</v>
+        <v>6.3025613857953</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07916301444083686</v>
+        <v>0.07905966658170452</v>
       </c>
       <c r="C65">
-        <v>42.8050369711525</v>
+        <v>41.75659722597581</v>
       </c>
       <c r="D65">
-        <v>105.8948218618578</v>
+        <v>105.9420929879622</v>
       </c>
       <c r="E65">
-        <v>44.05869776260161</v>
+        <v>45.15440863388265</v>
       </c>
       <c r="F65">
-        <v>69.02978489070534</v>
+        <v>70.12549576198639</v>
       </c>
       <c r="G65">
         <v>5.94</v>
@@ -6605,28 +6605,28 @@
         <v>23.624</v>
       </c>
       <c r="M65">
-        <v>3.7483173195653</v>
+        <v>3.807814419875861</v>
       </c>
       <c r="N65">
-        <v>19.8756826804347</v>
+        <v>19.81618558012414</v>
       </c>
       <c r="O65">
-        <v>3.975136536086941</v>
+        <v>3.963237116024828</v>
       </c>
       <c r="P65">
-        <v>15.90054614434776</v>
+        <v>15.85294846409931</v>
       </c>
       <c r="Q65">
-        <v>21.83054614434776</v>
+        <v>21.78294846409931</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1399886876779375</v>
+        <v>0.1423835182825125</v>
       </c>
       <c r="T65">
-        <v>1.936618553969849</v>
+        <v>1.985858791802797</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>6.3025613857953</v>
+        <v>6.204083864142248</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07905966658170452</v>
+        <v>0.07947631872257216</v>
       </c>
       <c r="C66">
-        <v>41.75659722597581</v>
+        <v>40.47056784830285</v>
       </c>
       <c r="D66">
-        <v>105.9420929879622</v>
+        <v>105.7517744815703</v>
       </c>
       <c r="E66">
-        <v>45.15440863388265</v>
+        <v>46.2501195051637</v>
       </c>
       <c r="F66">
-        <v>70.12549576198639</v>
+        <v>71.22120663326743</v>
       </c>
       <c r="G66">
         <v>5.94</v>
@@ -6687,45 +6687,45 @@
         <v>23.624</v>
       </c>
       <c r="M66">
-        <v>3.807814419875861</v>
+        <v>3.938532726819689</v>
       </c>
       <c r="N66">
-        <v>19.81618558012414</v>
+        <v>19.68546727318031</v>
       </c>
       <c r="O66">
-        <v>3.963237116024828</v>
+        <v>3.937093454636063</v>
       </c>
       <c r="P66">
-        <v>15.85294846409931</v>
+        <v>15.74837381854425</v>
       </c>
       <c r="Q66">
-        <v>21.78294846409931</v>
+        <v>21.67837381854425</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1423835182825125</v>
+        <v>0.1449151963502062</v>
       </c>
       <c r="T66">
-        <v>1.985858791802797</v>
+        <v>2.037912757511914</v>
       </c>
       <c r="U66">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V66">
         <v>0.2</v>
       </c>
       <c r="W66">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>6.204083864142248</v>
+        <v>5.998172832012002</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07947631872257216</v>
+        <v>0.0793809708634398</v>
       </c>
       <c r="C67">
-        <v>40.47056784830285</v>
+        <v>39.41834964406893</v>
       </c>
       <c r="D67">
-        <v>105.7517744815703</v>
+        <v>105.7952671486174</v>
       </c>
       <c r="E67">
-        <v>46.2501195051637</v>
+        <v>47.34583037644472</v>
       </c>
       <c r="F67">
-        <v>71.22120663326743</v>
+        <v>72.31691750454846</v>
       </c>
       <c r="G67">
         <v>5.94</v>
@@ -6769,28 +6769,28 @@
         <v>23.624</v>
       </c>
       <c r="M67">
-        <v>3.938532726819689</v>
+        <v>3.99912553800153</v>
       </c>
       <c r="N67">
-        <v>19.68546727318031</v>
+        <v>19.62487446199847</v>
       </c>
       <c r="O67">
-        <v>3.937093454636063</v>
+        <v>3.924974892399695</v>
       </c>
       <c r="P67">
-        <v>15.74837381854425</v>
+        <v>15.69989956959878</v>
       </c>
       <c r="Q67">
-        <v>21.67837381854425</v>
+        <v>21.62989956959878</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1449151963502062</v>
+        <v>0.1475957966571759</v>
       </c>
       <c r="T67">
-        <v>2.037912757511914</v>
+        <v>2.09302872120392</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.998172832012002</v>
+        <v>5.907291425466366</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0793809708634398</v>
+        <v>0.07928562300430746</v>
       </c>
       <c r="C68">
-        <v>39.41834964406893</v>
+        <v>38.36616722912326</v>
       </c>
       <c r="D68">
-        <v>105.7952671486174</v>
+        <v>105.8387956049528</v>
       </c>
       <c r="E68">
-        <v>47.34583037644472</v>
+        <v>48.44154124772577</v>
       </c>
       <c r="F68">
-        <v>72.31691750454846</v>
+        <v>73.4126283758295</v>
       </c>
       <c r="G68">
         <v>5.94</v>
@@ -6851,28 +6851,28 @@
         <v>23.624</v>
       </c>
       <c r="M68">
-        <v>3.99912553800153</v>
+        <v>4.059718349183371</v>
       </c>
       <c r="N68">
-        <v>19.62487446199847</v>
+        <v>19.56428165081663</v>
       </c>
       <c r="O68">
-        <v>3.924974892399695</v>
+        <v>3.912856330163327</v>
       </c>
       <c r="P68">
-        <v>15.69989956959878</v>
+        <v>15.65142532065331</v>
       </c>
       <c r="Q68">
-        <v>21.62989956959878</v>
+        <v>21.58142532065331</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1475957966571759</v>
+        <v>0.1504388575888105</v>
       </c>
       <c r="T68">
-        <v>2.09302872120392</v>
+        <v>2.151485046331805</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.907291425466366</v>
+        <v>5.819122896728062</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07928562300430746</v>
+        <v>0.0791902751451751</v>
       </c>
       <c r="C69">
-        <v>38.36616722912326</v>
+        <v>37.31402064765956</v>
       </c>
       <c r="D69">
-        <v>105.8387956049528</v>
+        <v>105.8823598947701</v>
       </c>
       <c r="E69">
-        <v>48.44154124772577</v>
+        <v>49.53725211900681</v>
       </c>
       <c r="F69">
-        <v>73.4126283758295</v>
+        <v>74.50833924711054</v>
       </c>
       <c r="G69">
         <v>5.94</v>
@@ -6933,28 +6933,28 @@
         <v>23.624</v>
       </c>
       <c r="M69">
-        <v>4.059718349183371</v>
+        <v>4.120311160365213</v>
       </c>
       <c r="N69">
-        <v>19.56428165081663</v>
+        <v>19.50368883963479</v>
       </c>
       <c r="O69">
-        <v>3.912856330163327</v>
+        <v>3.900737767926958</v>
       </c>
       <c r="P69">
-        <v>15.65142532065331</v>
+        <v>15.60295107170783</v>
       </c>
       <c r="Q69">
-        <v>21.58142532065331</v>
+        <v>21.53295107170783</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1504388575888105</v>
+        <v>0.1534596098286722</v>
       </c>
       <c r="T69">
-        <v>2.151485046331805</v>
+        <v>2.213594891780182</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.819122896728062</v>
+        <v>5.733547560011472</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0791902751451751</v>
+        <v>0.07909492728604275</v>
       </c>
       <c r="C70">
-        <v>37.31402064765956</v>
+        <v>36.26190994394433</v>
       </c>
       <c r="D70">
-        <v>105.8823598947701</v>
+        <v>105.9259600623359</v>
       </c>
       <c r="E70">
-        <v>49.53725211900681</v>
+        <v>50.63296299028785</v>
       </c>
       <c r="F70">
-        <v>74.50833924711054</v>
+        <v>75.60405011839158</v>
       </c>
       <c r="G70">
         <v>5.94</v>
@@ -7015,28 +7015,28 @@
         <v>23.624</v>
       </c>
       <c r="M70">
-        <v>4.120311160365213</v>
+        <v>4.180903971547055</v>
       </c>
       <c r="N70">
-        <v>19.50368883963479</v>
+        <v>19.44309602845295</v>
       </c>
       <c r="O70">
-        <v>3.900737767926958</v>
+        <v>3.88861920569059</v>
       </c>
       <c r="P70">
-        <v>15.60295107170783</v>
+        <v>15.55447682276236</v>
       </c>
       <c r="Q70">
-        <v>21.53295107170783</v>
+        <v>21.48447682276236</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1534596098286722</v>
+        <v>0.1566752493098154</v>
       </c>
       <c r="T70">
-        <v>2.213594891780182</v>
+        <v>2.279711824031681</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.733547560011472</v>
+        <v>5.650452667837392</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07909492728604275</v>
+        <v>0.0789995794269104</v>
       </c>
       <c r="C71">
-        <v>36.26190994394433</v>
+        <v>35.20983516231692</v>
       </c>
       <c r="D71">
-        <v>105.9259600623359</v>
+        <v>105.9695961519895</v>
       </c>
       <c r="E71">
-        <v>50.63296299028785</v>
+        <v>51.72867386156888</v>
       </c>
       <c r="F71">
-        <v>75.60405011839158</v>
+        <v>76.69976098967261</v>
       </c>
       <c r="G71">
         <v>5.94</v>
@@ -7097,28 +7097,28 @@
         <v>23.624</v>
       </c>
       <c r="M71">
-        <v>4.180903971547055</v>
+        <v>4.241496782728896</v>
       </c>
       <c r="N71">
-        <v>19.44309602845295</v>
+        <v>19.38250321727111</v>
       </c>
       <c r="O71">
-        <v>3.88861920569059</v>
+        <v>3.876500643454222</v>
       </c>
       <c r="P71">
-        <v>15.55447682276236</v>
+        <v>15.50600257381689</v>
       </c>
       <c r="Q71">
-        <v>21.48447682276236</v>
+        <v>21.43600257381689</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1566752493098154</v>
+        <v>0.160105264756368</v>
       </c>
       <c r="T71">
-        <v>2.279711824031681</v>
+        <v>2.350236551766613</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.650452667837392</v>
+        <v>5.569731915439716</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0789995794269104</v>
+        <v>0.07890423156777807</v>
       </c>
       <c r="C72">
-        <v>35.20983516231692</v>
+        <v>34.15779634718984</v>
       </c>
       <c r="D72">
-        <v>105.9695961519895</v>
+        <v>106.0132682081435</v>
       </c>
       <c r="E72">
-        <v>51.72867386156888</v>
+        <v>52.82438473284992</v>
       </c>
       <c r="F72">
-        <v>76.69976098967261</v>
+        <v>77.79547186095365</v>
       </c>
       <c r="G72">
         <v>5.94</v>
@@ -7179,28 +7179,28 @@
         <v>23.624</v>
       </c>
       <c r="M72">
-        <v>4.241496782728896</v>
+        <v>4.302089593910737</v>
       </c>
       <c r="N72">
-        <v>19.38250321727111</v>
+        <v>19.32191040608927</v>
       </c>
       <c r="O72">
-        <v>3.876500643454222</v>
+        <v>3.864382081217853</v>
       </c>
       <c r="P72">
-        <v>15.50600257381689</v>
+        <v>15.45752832487141</v>
       </c>
       <c r="Q72">
-        <v>21.43600257381689</v>
+        <v>21.38752832487141</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.160105264756368</v>
+        <v>0.1637718329923382</v>
       </c>
       <c r="T72">
-        <v>2.350236551766613</v>
+        <v>2.425625053828093</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.569731915439716</v>
+        <v>5.49128498705324</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07890423156777805</v>
+        <v>0.07880888370864571</v>
       </c>
       <c r="C73">
-        <v>34.15779634718987</v>
+        <v>33.10579354304886</v>
       </c>
       <c r="D73">
-        <v>106.0132682081435</v>
+        <v>106.0569762752835</v>
       </c>
       <c r="E73">
-        <v>52.82438473284991</v>
+        <v>53.92009560413095</v>
       </c>
       <c r="F73">
-        <v>77.79547186095364</v>
+        <v>78.89118273223468</v>
       </c>
       <c r="G73">
         <v>5.94</v>
@@ -7261,28 +7261,28 @@
         <v>23.624</v>
       </c>
       <c r="M73">
-        <v>4.302089593910736</v>
+        <v>4.362682405092578</v>
       </c>
       <c r="N73">
-        <v>19.32191040608927</v>
+        <v>19.26131759490742</v>
       </c>
       <c r="O73">
-        <v>3.864382081217853</v>
+        <v>3.852263518981485</v>
       </c>
       <c r="P73">
-        <v>15.45752832487141</v>
+        <v>15.40905407592594</v>
       </c>
       <c r="Q73">
-        <v>21.38752832487141</v>
+        <v>21.33905407592594</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1637718329923381</v>
+        <v>0.1677002989594489</v>
       </c>
       <c r="T73">
-        <v>2.425625053828092</v>
+        <v>2.506398448893962</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.491284987053241</v>
+        <v>5.415017140010836</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07880888370864571</v>
+        <v>0.07871353584951335</v>
       </c>
       <c r="C74">
-        <v>33.10579354304886</v>
+        <v>32.05382679445307</v>
       </c>
       <c r="D74">
-        <v>106.0569762752835</v>
+        <v>106.1007203979688</v>
       </c>
       <c r="E74">
-        <v>53.92009560413095</v>
+        <v>55.01580647541199</v>
       </c>
       <c r="F74">
-        <v>78.89118273223468</v>
+        <v>79.98689360351572</v>
       </c>
       <c r="G74">
         <v>5.94</v>
@@ -7343,28 +7343,28 @@
         <v>23.624</v>
       </c>
       <c r="M74">
-        <v>4.362682405092578</v>
+        <v>4.42327521627442</v>
       </c>
       <c r="N74">
-        <v>19.26131759490742</v>
+        <v>19.20072478372558</v>
       </c>
       <c r="O74">
-        <v>3.852263518981485</v>
+        <v>3.840144956745117</v>
       </c>
       <c r="P74">
-        <v>15.40905407592594</v>
+        <v>15.36057982698047</v>
       </c>
       <c r="Q74">
-        <v>21.33905407592594</v>
+        <v>21.29057982698047</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1677002989594489</v>
+        <v>0.171919762405605</v>
       </c>
       <c r="T74">
-        <v>2.506398448893962</v>
+        <v>2.593155058409156</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.415017140010836</v>
+        <v>5.340838823024384</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07871353584951335</v>
+        <v>0.07861818799038101</v>
       </c>
       <c r="C75">
-        <v>32.05382679445307</v>
+        <v>31.00189614603516</v>
       </c>
       <c r="D75">
-        <v>106.1007203979688</v>
+        <v>106.1445006208319</v>
       </c>
       <c r="E75">
-        <v>55.01580647541199</v>
+        <v>56.11151734669302</v>
       </c>
       <c r="F75">
-        <v>79.98689360351572</v>
+        <v>81.08260447479675</v>
       </c>
       <c r="G75">
         <v>5.94</v>
@@ -7425,28 +7425,28 @@
         <v>23.624</v>
       </c>
       <c r="M75">
-        <v>4.42327521627442</v>
+        <v>4.483868027456261</v>
       </c>
       <c r="N75">
-        <v>19.20072478372558</v>
+        <v>19.14013197254374</v>
       </c>
       <c r="O75">
-        <v>3.840144956745117</v>
+        <v>3.828026394508749</v>
       </c>
       <c r="P75">
-        <v>15.36057982698047</v>
+        <v>15.31210557803499</v>
       </c>
       <c r="Q75">
-        <v>21.29057982698047</v>
+        <v>21.24210557803499</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.171919762405605</v>
+        <v>0.1764637999630039</v>
       </c>
       <c r="T75">
-        <v>2.593155058409156</v>
+        <v>2.686585253271674</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.340838823024384</v>
+        <v>5.268665325415948</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07861818799038101</v>
+        <v>0.07852284013124866</v>
       </c>
       <c r="C76">
-        <v>31.00189614603516</v>
+        <v>29.95000164250152</v>
       </c>
       <c r="D76">
-        <v>106.1445006208319</v>
+        <v>106.1883169885793</v>
       </c>
       <c r="E76">
-        <v>56.11151734669302</v>
+        <v>57.20722821797406</v>
       </c>
       <c r="F76">
-        <v>81.08260447479675</v>
+        <v>82.1783153460778</v>
       </c>
       <c r="G76">
         <v>5.94</v>
@@ -7507,28 +7507,28 @@
         <v>23.624</v>
       </c>
       <c r="M76">
-        <v>4.483868027456261</v>
+        <v>4.544460838638102</v>
       </c>
       <c r="N76">
-        <v>19.14013197254374</v>
+        <v>19.0795391613619</v>
       </c>
       <c r="O76">
-        <v>3.828026394508749</v>
+        <v>3.81590783227238</v>
       </c>
       <c r="P76">
-        <v>15.31210557803499</v>
+        <v>15.26363132908952</v>
       </c>
       <c r="Q76">
-        <v>21.24210557803499</v>
+        <v>21.19363132908952</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1764637999630039</v>
+        <v>0.1813713605249946</v>
       </c>
       <c r="T76">
-        <v>2.686585253271674</v>
+        <v>2.787489863723192</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.268665325415948</v>
+        <v>5.198416454410402</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07852284013124866</v>
+        <v>0.07842749227211632</v>
       </c>
       <c r="C77">
-        <v>29.95000164250152</v>
+        <v>28.89814332863236</v>
       </c>
       <c r="D77">
-        <v>106.1883169885793</v>
+        <v>106.2321695459912</v>
       </c>
       <c r="E77">
-        <v>57.20722821797406</v>
+        <v>58.3029390892551</v>
       </c>
       <c r="F77">
-        <v>82.1783153460778</v>
+        <v>83.27402621735884</v>
       </c>
       <c r="G77">
         <v>5.94</v>
@@ -7589,28 +7589,28 @@
         <v>23.624</v>
       </c>
       <c r="M77">
-        <v>4.544460838638102</v>
+        <v>4.605053649819943</v>
       </c>
       <c r="N77">
-        <v>19.0795391613619</v>
+        <v>19.01894635018006</v>
       </c>
       <c r="O77">
-        <v>3.81590783227238</v>
+        <v>3.803789270036012</v>
       </c>
       <c r="P77">
-        <v>15.26363132908952</v>
+        <v>15.21515708014405</v>
       </c>
       <c r="Q77">
-        <v>21.19363132908952</v>
+        <v>21.14515708014405</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1813713605249946</v>
+        <v>0.1866878844671513</v>
       </c>
       <c r="T77">
-        <v>2.787489863723192</v>
+        <v>2.896803191712337</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.198416454410402</v>
+        <v>5.130016237905002</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07842749227211632</v>
+        <v>0.07833214441298396</v>
       </c>
       <c r="C78">
-        <v>28.89814332863236</v>
+        <v>27.84632124928196</v>
       </c>
       <c r="D78">
-        <v>106.2321695459912</v>
+        <v>106.2760583379218</v>
       </c>
       <c r="E78">
-        <v>58.3029390892551</v>
+        <v>59.39864996053613</v>
       </c>
       <c r="F78">
-        <v>83.27402621735884</v>
+        <v>84.36973708863987</v>
       </c>
       <c r="G78">
         <v>5.94</v>
@@ -7671,28 +7671,28 @@
         <v>23.624</v>
       </c>
       <c r="M78">
-        <v>4.605053649819943</v>
+        <v>4.665646461001785</v>
       </c>
       <c r="N78">
-        <v>19.01894635018006</v>
+        <v>18.95835353899822</v>
       </c>
       <c r="O78">
-        <v>3.803789270036012</v>
+        <v>3.791670707799644</v>
       </c>
       <c r="P78">
-        <v>15.21515708014405</v>
+        <v>15.16668283119857</v>
       </c>
       <c r="Q78">
-        <v>21.14515708014405</v>
+        <v>21.09668283119857</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1866878844671513</v>
+        <v>0.1924667148390607</v>
       </c>
       <c r="T78">
-        <v>2.896803191712337</v>
+        <v>3.015622026483147</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.130016237905002</v>
+        <v>5.063392650399742</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07833214441298396</v>
+        <v>0.0782367965538516</v>
       </c>
       <c r="C79">
-        <v>27.84632124928196</v>
+        <v>26.79453544937861</v>
       </c>
       <c r="D79">
-        <v>106.2760583379218</v>
+        <v>106.3199834092995</v>
       </c>
       <c r="E79">
-        <v>59.39864996053613</v>
+        <v>60.49436083181718</v>
       </c>
       <c r="F79">
-        <v>84.36973708863987</v>
+        <v>85.46544795992091</v>
       </c>
       <c r="G79">
         <v>5.94</v>
@@ -7753,28 +7753,28 @@
         <v>23.624</v>
       </c>
       <c r="M79">
-        <v>4.665646461001785</v>
+        <v>4.726239272183626</v>
       </c>
       <c r="N79">
-        <v>18.95835353899822</v>
+        <v>18.89776072781638</v>
       </c>
       <c r="O79">
-        <v>3.791670707799644</v>
+        <v>3.779552145563275</v>
       </c>
       <c r="P79">
-        <v>15.16668283119857</v>
+        <v>15.1182085822531</v>
       </c>
       <c r="Q79">
-        <v>21.09668283119857</v>
+        <v>21.0482085822531</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1924667148390607</v>
+        <v>0.1987708934265982</v>
       </c>
       <c r="T79">
-        <v>3.015622026483147</v>
+        <v>3.145242573505848</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.063392650399742</v>
+        <v>4.998477360010002</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0782367965538516</v>
+        <v>0.07814144869471926</v>
       </c>
       <c r="C80">
-        <v>26.79453544937861</v>
+        <v>25.74278597392505</v>
       </c>
       <c r="D80">
-        <v>106.3199834092995</v>
+        <v>106.363944805127</v>
       </c>
       <c r="E80">
-        <v>60.49436083181718</v>
+        <v>61.59007170309822</v>
       </c>
       <c r="F80">
-        <v>85.46544795992091</v>
+        <v>86.56115883120195</v>
       </c>
       <c r="G80">
         <v>5.94</v>
@@ -7835,28 +7835,28 @@
         <v>23.624</v>
       </c>
       <c r="M80">
-        <v>4.726239272183626</v>
+        <v>4.786832083365468</v>
       </c>
       <c r="N80">
-        <v>18.89776072781638</v>
+        <v>18.83716791663453</v>
       </c>
       <c r="O80">
-        <v>3.779552145563275</v>
+        <v>3.767433583326907</v>
       </c>
       <c r="P80">
-        <v>15.1182085822531</v>
+        <v>15.06973433330763</v>
       </c>
       <c r="Q80">
-        <v>21.0482085822531</v>
+        <v>20.99973433330763</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1987708934265982</v>
+        <v>0.2056754699748536</v>
       </c>
       <c r="T80">
-        <v>3.145242573505848</v>
+        <v>3.287207934530712</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.998477360010002</v>
+        <v>4.935205494693419</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07814144869471926</v>
+        <v>0.07804610083558691</v>
       </c>
       <c r="C81">
-        <v>25.74278597392505</v>
+        <v>24.69107286799846</v>
       </c>
       <c r="D81">
-        <v>106.363944805127</v>
+        <v>106.4079425704815</v>
       </c>
       <c r="E81">
-        <v>61.59007170309822</v>
+        <v>62.68578257437926</v>
       </c>
       <c r="F81">
-        <v>86.56115883120195</v>
+        <v>87.65686970248299</v>
       </c>
       <c r="G81">
         <v>5.94</v>
@@ -7917,28 +7917,28 @@
         <v>23.624</v>
       </c>
       <c r="M81">
-        <v>4.786832083365468</v>
+        <v>4.847424894547309</v>
       </c>
       <c r="N81">
-        <v>18.83716791663453</v>
+        <v>18.77657510545269</v>
       </c>
       <c r="O81">
-        <v>3.767433583326907</v>
+        <v>3.755315021090539</v>
       </c>
       <c r="P81">
-        <v>15.06973433330763</v>
+        <v>15.02126008436215</v>
       </c>
       <c r="Q81">
-        <v>20.99973433330763</v>
+        <v>20.95126008436215</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2056754699748536</v>
+        <v>0.2132705041779346</v>
       </c>
       <c r="T81">
-        <v>3.287207934530712</v>
+        <v>3.443369831658062</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.935205494693419</v>
+        <v>4.873515426009751</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07804610083558691</v>
+        <v>0.07795075297645457</v>
       </c>
       <c r="C82">
-        <v>24.69107286799846</v>
+        <v>23.63939617675058</v>
       </c>
       <c r="D82">
-        <v>106.4079425704815</v>
+        <v>106.4519767505146</v>
       </c>
       <c r="E82">
-        <v>62.68578257437926</v>
+        <v>63.78149344566029</v>
       </c>
       <c r="F82">
-        <v>87.65686970248299</v>
+        <v>88.75258057376402</v>
       </c>
       <c r="G82">
         <v>5.94</v>
@@ -7999,28 +7999,28 @@
         <v>23.624</v>
       </c>
       <c r="M82">
-        <v>4.847424894547309</v>
+        <v>4.908017705729151</v>
       </c>
       <c r="N82">
-        <v>18.77657510545269</v>
+        <v>18.71598229427085</v>
       </c>
       <c r="O82">
-        <v>3.755315021090539</v>
+        <v>3.74319645885417</v>
       </c>
       <c r="P82">
-        <v>15.02126008436215</v>
+        <v>14.97278583541668</v>
       </c>
       <c r="Q82">
-        <v>20.95126008436215</v>
+        <v>20.90278583541668</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2132705041779346</v>
+        <v>0.2216650156655504</v>
       </c>
       <c r="T82">
-        <v>3.443369831658062</v>
+        <v>3.61596982321987</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.873515426009751</v>
+        <v>4.813348568898519</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07795075297645457</v>
+        <v>0.07785540511732221</v>
       </c>
       <c r="C83">
-        <v>23.63939617675058</v>
+        <v>22.58775594540792</v>
       </c>
       <c r="D83">
-        <v>106.4519767505146</v>
+        <v>106.496047390453</v>
       </c>
       <c r="E83">
-        <v>63.78149344566029</v>
+        <v>64.87720431694133</v>
       </c>
       <c r="F83">
-        <v>88.75258057376402</v>
+        <v>89.84829144504506</v>
       </c>
       <c r="G83">
         <v>5.94</v>
@@ -8081,28 +8081,28 @@
         <v>23.624</v>
       </c>
       <c r="M83">
-        <v>4.908017705729151</v>
+        <v>4.968610516910992</v>
       </c>
       <c r="N83">
-        <v>18.71598229427085</v>
+        <v>18.65538948308901</v>
       </c>
       <c r="O83">
-        <v>3.74319645885417</v>
+        <v>3.731077896617802</v>
       </c>
       <c r="P83">
-        <v>14.97278583541668</v>
+        <v>14.92431158647121</v>
       </c>
       <c r="Q83">
-        <v>20.90278583541668</v>
+        <v>20.85431158647121</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2216650156655504</v>
+        <v>0.2309922506517901</v>
       </c>
       <c r="T83">
-        <v>3.61596982321987</v>
+        <v>3.807747591621878</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.813348568898519</v>
+        <v>4.754649196107074</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07785540511732221</v>
+        <v>0.07776005725818987</v>
       </c>
       <c r="C84">
-        <v>22.58775594540792</v>
+        <v>21.53615221927201</v>
       </c>
       <c r="D84">
-        <v>106.496047390453</v>
+        <v>106.5401545355981</v>
       </c>
       <c r="E84">
-        <v>64.87720431694133</v>
+        <v>65.97291518822237</v>
       </c>
       <c r="F84">
-        <v>89.84829144504506</v>
+        <v>90.94400231632611</v>
       </c>
       <c r="G84">
         <v>5.94</v>
@@ -8163,28 +8163,28 @@
         <v>23.624</v>
       </c>
       <c r="M84">
-        <v>4.968610516910992</v>
+        <v>5.029203328092834</v>
       </c>
       <c r="N84">
-        <v>18.65538948308901</v>
+        <v>18.59479667190717</v>
       </c>
       <c r="O84">
-        <v>3.731077896617802</v>
+        <v>3.718959334381434</v>
       </c>
       <c r="P84">
-        <v>14.92431158647121</v>
+        <v>14.87583733752573</v>
       </c>
       <c r="Q84">
-        <v>20.85431158647121</v>
+        <v>20.80583733752573</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2309922506517901</v>
+        <v>0.2414168074011169</v>
       </c>
       <c r="T84">
-        <v>3.807747591621878</v>
+        <v>4.022087450424123</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>4.754649196107074</v>
+        <v>4.697364266033494</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07776005725818987</v>
+        <v>0.07766470939905751</v>
       </c>
       <c r="C85">
-        <v>21.53615221927201</v>
+        <v>20.48458504371938</v>
       </c>
       <c r="D85">
-        <v>106.5401545355981</v>
+        <v>106.5842982313265</v>
       </c>
       <c r="E85">
-        <v>65.97291518822237</v>
+        <v>67.0686260595034</v>
       </c>
       <c r="F85">
-        <v>90.94400231632611</v>
+        <v>92.03971318760713</v>
       </c>
       <c r="G85">
         <v>5.94</v>
@@ -8245,28 +8245,28 @@
         <v>23.624</v>
       </c>
       <c r="M85">
-        <v>5.029203328092834</v>
+        <v>5.089796139274675</v>
       </c>
       <c r="N85">
-        <v>18.59479667190717</v>
+        <v>18.53420386072533</v>
       </c>
       <c r="O85">
-        <v>3.718959334381434</v>
+        <v>3.706840772145066</v>
       </c>
       <c r="P85">
-        <v>14.87583733752573</v>
+        <v>14.82736308858026</v>
       </c>
       <c r="Q85">
-        <v>20.80583733752573</v>
+        <v>20.75736308858026</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2414168074011169</v>
+        <v>0.2531444337441096</v>
       </c>
       <c r="T85">
-        <v>4.022087450424123</v>
+        <v>4.263219791576649</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.697364266033494</v>
+        <v>4.64144326286643</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07766470939905751</v>
+        <v>0.07756936153992516</v>
       </c>
       <c r="C86">
-        <v>20.48458504371938</v>
+        <v>19.43305446420179</v>
       </c>
       <c r="D86">
-        <v>106.5842982313265</v>
+        <v>106.62847852309</v>
       </c>
       <c r="E86">
-        <v>67.0686260595034</v>
+        <v>68.16433693078443</v>
       </c>
       <c r="F86">
-        <v>92.03971318760713</v>
+        <v>93.13542405888816</v>
       </c>
       <c r="G86">
         <v>5.94</v>
@@ -8327,28 +8327,28 @@
         <v>23.624</v>
       </c>
       <c r="M86">
-        <v>5.089796139274675</v>
+        <v>5.150388950456516</v>
       </c>
       <c r="N86">
-        <v>18.53420386072533</v>
+        <v>18.47361104954349</v>
       </c>
       <c r="O86">
-        <v>3.706840772145066</v>
+        <v>3.694722209908697</v>
       </c>
       <c r="P86">
-        <v>14.82736308858026</v>
+        <v>14.77888883963479</v>
       </c>
       <c r="Q86">
-        <v>20.75736308858026</v>
+        <v>20.70888883963479</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2531444337441094</v>
+        <v>0.2664357435995011</v>
       </c>
       <c r="T86">
-        <v>4.263219791576646</v>
+        <v>4.536503111549509</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.64144326286643</v>
+        <v>4.586838048009177</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07756936153992516</v>
+        <v>0.07747401368079282</v>
       </c>
       <c r="C87">
-        <v>19.43305446420179</v>
+        <v>18.3815605262464</v>
       </c>
       <c r="D87">
-        <v>106.62847852309</v>
+        <v>106.6726954564156</v>
       </c>
       <c r="E87">
-        <v>68.16433693078443</v>
+        <v>69.26004780206547</v>
       </c>
       <c r="F87">
-        <v>93.13542405888816</v>
+        <v>94.2311349301692</v>
       </c>
       <c r="G87">
         <v>5.94</v>
@@ -8409,28 +8409,28 @@
         <v>23.624</v>
       </c>
       <c r="M87">
-        <v>5.150388950456516</v>
+        <v>5.210981761638357</v>
       </c>
       <c r="N87">
-        <v>18.47361104954349</v>
+        <v>18.41301823836164</v>
       </c>
       <c r="O87">
-        <v>3.694722209908697</v>
+        <v>3.682603647672329</v>
       </c>
       <c r="P87">
-        <v>14.77888883963479</v>
+        <v>14.73041459068932</v>
       </c>
       <c r="Q87">
-        <v>20.70888883963479</v>
+        <v>20.66041459068931</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2664357435995011</v>
+        <v>0.2816258120056629</v>
       </c>
       <c r="T87">
-        <v>4.536503111549509</v>
+        <v>4.848826905804208</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.586838048009177</v>
+        <v>4.533502721869536</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07747401368079282</v>
+        <v>0.07911866582166047</v>
       </c>
       <c r="C88">
-        <v>18.3815605262464</v>
+        <v>16.52825587148648</v>
       </c>
       <c r="D88">
-        <v>106.6726954564156</v>
+        <v>105.9151016729367</v>
       </c>
       <c r="E88">
-        <v>69.26004780206547</v>
+        <v>70.35575867334651</v>
       </c>
       <c r="F88">
-        <v>94.2311349301692</v>
+        <v>95.32684580145025</v>
       </c>
       <c r="G88">
         <v>5.94</v>
@@ -8491,45 +8491,45 @@
         <v>23.624</v>
       </c>
       <c r="M88">
-        <v>5.210981761638357</v>
+        <v>5.509891687323825</v>
       </c>
       <c r="N88">
-        <v>18.41301823836164</v>
+        <v>18.11410831267618</v>
       </c>
       <c r="O88">
-        <v>3.682603647672329</v>
+        <v>3.622821662535236</v>
       </c>
       <c r="P88">
-        <v>14.73041459068932</v>
+        <v>14.49128665014094</v>
       </c>
       <c r="Q88">
-        <v>20.66041459068931</v>
+        <v>20.42128665014094</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2816258120056629</v>
+        <v>0.2991528140127727</v>
       </c>
       <c r="T88">
-        <v>4.848826905804208</v>
+        <v>5.20920051455963</v>
       </c>
       <c r="U88">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V88">
         <v>0.2</v>
       </c>
       <c r="W88">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y88">
-        <v>4.533502721869536</v>
+        <v>4.28756159660087</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07911866582166047</v>
+        <v>0.07904331796252811</v>
       </c>
       <c r="C89">
-        <v>16.52825587148648</v>
+        <v>15.46701801083515</v>
       </c>
       <c r="D89">
-        <v>105.9151016729367</v>
+        <v>105.9495746835664</v>
       </c>
       <c r="E89">
-        <v>70.35575867334651</v>
+        <v>71.45146954462754</v>
       </c>
       <c r="F89">
-        <v>95.32684580145025</v>
+        <v>96.42255667273128</v>
       </c>
       <c r="G89">
         <v>5.94</v>
@@ -8573,28 +8573,28 @@
         <v>23.624</v>
       </c>
       <c r="M89">
-        <v>5.509891687323825</v>
+        <v>5.573223775683868</v>
       </c>
       <c r="N89">
-        <v>18.11410831267618</v>
+        <v>18.05077622431613</v>
       </c>
       <c r="O89">
-        <v>3.622821662535236</v>
+        <v>3.610155244863227</v>
       </c>
       <c r="P89">
-        <v>14.49128665014094</v>
+        <v>14.44062097945291</v>
       </c>
       <c r="Q89">
-        <v>20.42128665014094</v>
+        <v>20.37062097945291</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2991528140127727</v>
+        <v>0.3196009830210676</v>
       </c>
       <c r="T89">
-        <v>5.20920051455963</v>
+        <v>5.629636391440957</v>
       </c>
       <c r="U89">
         <v>0.0578</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.28756159660087</v>
+        <v>4.238839305730407</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07904331796252811</v>
+        <v>0.07896797010339576</v>
       </c>
       <c r="C90">
-        <v>15.46701801083515</v>
+        <v>14.40580259788699</v>
       </c>
       <c r="D90">
-        <v>105.9495746835664</v>
+        <v>105.9840701418993</v>
       </c>
       <c r="E90">
-        <v>71.45146954462754</v>
+        <v>72.54718041590858</v>
       </c>
       <c r="F90">
-        <v>96.42255667273128</v>
+        <v>97.51826754401232</v>
       </c>
       <c r="G90">
         <v>5.94</v>
@@ -8655,28 +8655,28 @@
         <v>23.624</v>
       </c>
       <c r="M90">
-        <v>5.573223775683868</v>
+        <v>5.636555864043912</v>
       </c>
       <c r="N90">
-        <v>18.05077622431613</v>
+        <v>17.98744413595609</v>
       </c>
       <c r="O90">
-        <v>3.610155244863227</v>
+        <v>3.597488827191218</v>
       </c>
       <c r="P90">
-        <v>14.44062097945291</v>
+        <v>14.38995530876487</v>
       </c>
       <c r="Q90">
-        <v>20.37062097945291</v>
+        <v>20.31995530876487</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3196009830210676</v>
+        <v>0.3437670009399615</v>
       </c>
       <c r="T90">
-        <v>5.629636391440957</v>
+        <v>6.126515155027979</v>
       </c>
       <c r="U90">
         <v>0.0578</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.238839305730407</v>
+        <v>4.191211897800851</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07896797010339576</v>
+        <v>0.07889262224426342</v>
       </c>
       <c r="C91">
-        <v>14.40580259788699</v>
+        <v>13.34460965457494</v>
       </c>
       <c r="D91">
-        <v>105.9840701418993</v>
+        <v>106.0185880698683</v>
       </c>
       <c r="E91">
-        <v>72.54718041590858</v>
+        <v>73.64289128718963</v>
       </c>
       <c r="F91">
-        <v>97.51826754401232</v>
+        <v>98.61397841529336</v>
       </c>
       <c r="G91">
         <v>5.94</v>
@@ -8737,28 +8737,28 @@
         <v>23.624</v>
       </c>
       <c r="M91">
-        <v>5.636555864043912</v>
+        <v>5.699887952403957</v>
       </c>
       <c r="N91">
-        <v>17.98744413595609</v>
+        <v>17.92411204759605</v>
       </c>
       <c r="O91">
-        <v>3.597488827191218</v>
+        <v>3.58482240951921</v>
       </c>
       <c r="P91">
-        <v>14.38995530876487</v>
+        <v>14.33928963807684</v>
       </c>
       <c r="Q91">
-        <v>20.31995530876487</v>
+        <v>20.26928963807684</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3437670009399615</v>
+        <v>0.3727662224426342</v>
       </c>
       <c r="T91">
-        <v>6.126515155027979</v>
+        <v>6.722769671332407</v>
       </c>
       <c r="U91">
         <v>0.0578</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.191211897800851</v>
+        <v>4.144642876714174</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07889262224426342</v>
+        <v>0.07881727438513106</v>
       </c>
       <c r="C92">
-        <v>13.34460965457494</v>
+        <v>12.28343920286061</v>
       </c>
       <c r="D92">
-        <v>106.0185880698683</v>
+        <v>106.053128489435</v>
       </c>
       <c r="E92">
-        <v>73.64289128718963</v>
+        <v>74.73860215847066</v>
       </c>
       <c r="F92">
-        <v>98.61397841529336</v>
+        <v>99.70968928657439</v>
       </c>
       <c r="G92">
         <v>5.94</v>
@@ -8819,28 +8819,28 @@
         <v>23.624</v>
       </c>
       <c r="M92">
-        <v>5.699887952403957</v>
+        <v>5.763220040764</v>
       </c>
       <c r="N92">
-        <v>17.92411204759605</v>
+        <v>17.860779959236</v>
       </c>
       <c r="O92">
-        <v>3.58482240951921</v>
+        <v>3.5721559918472</v>
       </c>
       <c r="P92">
-        <v>14.33928963807684</v>
+        <v>14.2886239673888</v>
       </c>
       <c r="Q92">
-        <v>20.26928963807684</v>
+        <v>20.2186239673888</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3727662224426342</v>
+        <v>0.4082097153903452</v>
       </c>
       <c r="T92">
-        <v>6.722769671332407</v>
+        <v>7.451525191260039</v>
       </c>
       <c r="U92">
         <v>0.0578</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.144642876714174</v>
+        <v>4.099097350596438</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07881727438513106</v>
+        <v>0.07874192652599871</v>
       </c>
       <c r="C93">
-        <v>12.28343920286061</v>
+        <v>11.22229126473411</v>
       </c>
       <c r="D93">
-        <v>106.053128489435</v>
+        <v>106.0876914225895</v>
       </c>
       <c r="E93">
-        <v>74.73860215847066</v>
+        <v>75.8343130297517</v>
       </c>
       <c r="F93">
-        <v>99.70968928657439</v>
+        <v>100.8054001578554</v>
       </c>
       <c r="G93">
         <v>5.94</v>
@@ -8901,28 +8901,28 @@
         <v>23.624</v>
       </c>
       <c r="M93">
-        <v>5.763220040764</v>
+        <v>5.826552129124044</v>
       </c>
       <c r="N93">
-        <v>17.860779959236</v>
+        <v>17.79744787087596</v>
       </c>
       <c r="O93">
-        <v>3.5721559918472</v>
+        <v>3.559489574175192</v>
       </c>
       <c r="P93">
-        <v>14.2886239673888</v>
+        <v>14.23795829670076</v>
       </c>
       <c r="Q93">
-        <v>20.2186239673888</v>
+        <v>20.16795829670076</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4082097153903452</v>
+        <v>0.4525140815749841</v>
       </c>
       <c r="T93">
-        <v>7.451525191260039</v>
+        <v>8.362469591169582</v>
       </c>
       <c r="U93">
         <v>0.0578</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.099097350596438</v>
+        <v>4.054541944611692</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07874192652599871</v>
+        <v>0.07866657866686635</v>
       </c>
       <c r="C94">
-        <v>11.22229126473411</v>
+        <v>10.1611658622143</v>
       </c>
       <c r="D94">
-        <v>106.0876914225895</v>
+        <v>106.1222768913508</v>
       </c>
       <c r="E94">
-        <v>75.8343130297517</v>
+        <v>76.93002390103274</v>
       </c>
       <c r="F94">
-        <v>100.8054001578554</v>
+        <v>101.9011110291365</v>
       </c>
       <c r="G94">
         <v>5.94</v>
@@ -8983,28 +8983,28 @@
         <v>23.624</v>
       </c>
       <c r="M94">
-        <v>5.826552129124044</v>
+        <v>5.889884217484089</v>
       </c>
       <c r="N94">
-        <v>17.79744787087596</v>
+        <v>17.73411578251591</v>
       </c>
       <c r="O94">
-        <v>3.559489574175192</v>
+        <v>3.546823156503183</v>
       </c>
       <c r="P94">
-        <v>14.23795829670076</v>
+        <v>14.18729262601273</v>
       </c>
       <c r="Q94">
-        <v>20.16795829670076</v>
+        <v>20.11729262601273</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4525140815749841</v>
+        <v>0.5094768380980912</v>
       </c>
       <c r="T94">
-        <v>8.362469591169582</v>
+        <v>9.533683819624706</v>
       </c>
       <c r="U94">
         <v>0.0578</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.054541944611692</v>
+        <v>4.010944719400815</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07866657866686635</v>
+        <v>0.081223230807734</v>
       </c>
       <c r="C95">
-        <v>10.1611658622143</v>
+        <v>7.904385508921834</v>
       </c>
       <c r="D95">
-        <v>106.1222768913508</v>
+        <v>104.9612074093394</v>
       </c>
       <c r="E95">
-        <v>76.93002390103274</v>
+        <v>78.02573477231378</v>
       </c>
       <c r="F95">
-        <v>101.9011110291365</v>
+        <v>102.9968219004175</v>
       </c>
       <c r="G95">
         <v>5.94</v>
@@ -9065,45 +9065,45 @@
         <v>23.624</v>
       </c>
       <c r="M95">
-        <v>5.889884217484089</v>
+        <v>6.313705182495593</v>
       </c>
       <c r="N95">
-        <v>17.73411578251591</v>
+        <v>17.31029481750441</v>
       </c>
       <c r="O95">
-        <v>3.546823156503183</v>
+        <v>3.462058963500882</v>
       </c>
       <c r="P95">
-        <v>14.18729262601273</v>
+        <v>13.84823585400353</v>
       </c>
       <c r="Q95">
-        <v>20.11729262601273</v>
+        <v>19.77823585400353</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5094768380980912</v>
+        <v>0.5854271801289006</v>
       </c>
       <c r="T95">
-        <v>9.533683819624706</v>
+        <v>11.09530279089821</v>
       </c>
       <c r="U95">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V95">
         <v>0.2</v>
       </c>
       <c r="W95">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y95">
-        <v>4.010944719400815</v>
+        <v>3.741701475940984</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.081223230807734</v>
+        <v>0.08117588294860167</v>
       </c>
       <c r="C96">
-        <v>7.904385508921834</v>
+        <v>6.829946091741533</v>
       </c>
       <c r="D96">
-        <v>104.9612074093394</v>
+        <v>104.9824788634401</v>
       </c>
       <c r="E96">
-        <v>78.02573477231378</v>
+        <v>79.12144564359481</v>
       </c>
       <c r="F96">
-        <v>102.9968219004175</v>
+        <v>104.0925327716985</v>
       </c>
       <c r="G96">
         <v>5.94</v>
@@ -9147,28 +9147,28 @@
         <v>23.624</v>
       </c>
       <c r="M96">
-        <v>6.313705182495593</v>
+        <v>6.380872258905121</v>
       </c>
       <c r="N96">
-        <v>17.31029481750441</v>
+        <v>17.24312774109488</v>
       </c>
       <c r="O96">
-        <v>3.462058963500882</v>
+        <v>3.448625548218976</v>
       </c>
       <c r="P96">
-        <v>13.84823585400353</v>
+        <v>13.79450219287591</v>
       </c>
       <c r="Q96">
-        <v>19.77823585400353</v>
+        <v>19.7245021928759</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5854271801289006</v>
+        <v>0.6917576589720341</v>
       </c>
       <c r="T96">
-        <v>11.09530279089821</v>
+        <v>13.28156935068111</v>
       </c>
       <c r="U96">
         <v>0.0613</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.741701475940984</v>
+        <v>3.70231514461529</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08117588294860167</v>
+        <v>0.08112853508946931</v>
       </c>
       <c r="C97">
-        <v>6.829946091741533</v>
+        <v>5.75551529806107</v>
       </c>
       <c r="D97">
-        <v>104.9824788634401</v>
+        <v>105.0037589410407</v>
       </c>
       <c r="E97">
-        <v>79.12144564359481</v>
+        <v>80.21715651487585</v>
       </c>
       <c r="F97">
-        <v>104.0925327716985</v>
+        <v>105.1882436429796</v>
       </c>
       <c r="G97">
         <v>5.94</v>
@@ -9229,28 +9229,28 @@
         <v>23.624</v>
       </c>
       <c r="M97">
-        <v>6.380872258905121</v>
+        <v>6.448039335314649</v>
       </c>
       <c r="N97">
-        <v>17.24312774109488</v>
+        <v>17.17596066468536</v>
       </c>
       <c r="O97">
-        <v>3.448625548218976</v>
+        <v>3.435192132937071</v>
       </c>
       <c r="P97">
-        <v>13.79450219287591</v>
+        <v>13.74076853174828</v>
       </c>
       <c r="Q97">
-        <v>19.7245021928759</v>
+        <v>19.67076853174828</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6917576589720341</v>
+        <v>0.8512533772367341</v>
       </c>
       <c r="T97">
-        <v>13.28156935068111</v>
+        <v>16.56096919035546</v>
       </c>
       <c r="U97">
         <v>0.0613</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.70231514461529</v>
+        <v>3.663749361858881</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08112853508946932</v>
+        <v>0.08108118723033697</v>
       </c>
       <c r="C98">
-        <v>5.755515298061084</v>
+        <v>4.681093133125472</v>
       </c>
       <c r="D98">
-        <v>105.0037589410407</v>
+        <v>105.0250476473861</v>
       </c>
       <c r="E98">
-        <v>80.21715651487584</v>
+        <v>81.31286738615688</v>
       </c>
       <c r="F98">
-        <v>105.1882436429796</v>
+        <v>106.2839545142606</v>
       </c>
       <c r="G98">
         <v>5.94</v>
@@ -9311,28 +9311,28 @@
         <v>23.624</v>
       </c>
       <c r="M98">
-        <v>6.448039335314648</v>
+        <v>6.515206411724176</v>
       </c>
       <c r="N98">
-        <v>17.17596066468536</v>
+        <v>17.10879358827583</v>
       </c>
       <c r="O98">
-        <v>3.435192132937071</v>
+        <v>3.421758717655166</v>
       </c>
       <c r="P98">
-        <v>13.74076853174828</v>
+        <v>13.68703487062066</v>
       </c>
       <c r="Q98">
-        <v>19.67076853174828</v>
+        <v>19.61703487062066</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8512533772367321</v>
+        <v>1.117079574344565</v>
       </c>
       <c r="T98">
-        <v>16.56096919035542</v>
+        <v>22.02663558981266</v>
       </c>
       <c r="U98">
         <v>0.0613</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.663749361858881</v>
+        <v>3.625978749880954</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08108118723033697</v>
+        <v>0.08103383937120462</v>
       </c>
       <c r="C99">
-        <v>4.681093133125472</v>
+        <v>3.606679602184045</v>
       </c>
       <c r="D99">
-        <v>105.0250476473861</v>
+        <v>105.0463449877257</v>
       </c>
       <c r="E99">
-        <v>81.31286738615688</v>
+        <v>82.40857825743792</v>
       </c>
       <c r="F99">
-        <v>106.2839545142606</v>
+        <v>107.3796653855417</v>
       </c>
       <c r="G99">
         <v>5.94</v>
@@ -9393,28 +9393,28 @@
         <v>23.624</v>
       </c>
       <c r="M99">
-        <v>6.515206411724176</v>
+        <v>6.582373488133704</v>
       </c>
       <c r="N99">
-        <v>17.10879358827583</v>
+        <v>17.0416265118663</v>
       </c>
       <c r="O99">
-        <v>3.421758717655166</v>
+        <v>3.40832530237326</v>
       </c>
       <c r="P99">
-        <v>13.68703487062066</v>
+        <v>13.63330120949304</v>
       </c>
       <c r="Q99">
-        <v>19.61703487062066</v>
+        <v>19.56330120949304</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.117079574344565</v>
+        <v>1.648731968560229</v>
       </c>
       <c r="T99">
-        <v>22.02663558981266</v>
+        <v>32.95796838872712</v>
       </c>
       <c r="U99">
         <v>0.0613</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.625978749880954</v>
+        <v>3.588978966718903</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08103383937120462</v>
+        <v>0.08098649151207227</v>
       </c>
       <c r="C100">
-        <v>3.606679602184045</v>
+        <v>2.532274710490356</v>
       </c>
       <c r="D100">
-        <v>105.0463449877257</v>
+        <v>105.067650967313</v>
       </c>
       <c r="E100">
-        <v>82.40857825743792</v>
+        <v>83.50428912871895</v>
       </c>
       <c r="F100">
-        <v>107.3796653855417</v>
+        <v>108.4753762568227</v>
       </c>
       <c r="G100">
         <v>5.94</v>
@@ -9475,28 +9475,28 @@
         <v>23.624</v>
       </c>
       <c r="M100">
-        <v>6.582373488133704</v>
+        <v>6.649540564543231</v>
       </c>
       <c r="N100">
-        <v>17.0416265118663</v>
+        <v>16.97445943545677</v>
       </c>
       <c r="O100">
-        <v>3.40832530237326</v>
+        <v>3.394891887091354</v>
       </c>
       <c r="P100">
-        <v>13.63330120949304</v>
+        <v>13.57956754836542</v>
       </c>
       <c r="Q100">
-        <v>19.56330120949304</v>
+        <v>19.50956754836542</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.648731968560229</v>
+        <v>3.243689151207223</v>
       </c>
       <c r="T100">
-        <v>32.95796838872712</v>
+        <v>65.75196678547053</v>
       </c>
       <c r="U100">
         <v>0.0613</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.588978966718903</v>
+        <v>3.552726653923763</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08098649151207227</v>
-      </c>
-      <c r="C101">
-        <v>2.532274710490356</v>
-      </c>
-      <c r="D101">
-        <v>105.067650967313</v>
-      </c>
-      <c r="E101">
-        <v>83.50428912871895</v>
-      </c>
-      <c r="F101">
-        <v>108.4753762568227</v>
-      </c>
-      <c r="G101">
-        <v>5.94</v>
-      </c>
-      <c r="H101">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>29.554</v>
-      </c>
-      <c r="K101">
-        <v>5.93</v>
-      </c>
-      <c r="L101">
-        <v>23.624</v>
-      </c>
-      <c r="M101">
-        <v>6.649540564543231</v>
-      </c>
-      <c r="N101">
-        <v>16.97445943545677</v>
-      </c>
-      <c r="O101">
-        <v>3.394891887091354</v>
-      </c>
-      <c r="P101">
-        <v>13.57956754836542</v>
-      </c>
-      <c r="Q101">
-        <v>19.50956754836542</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.243689151207223</v>
-      </c>
-      <c r="T101">
-        <v>65.75196678547053</v>
-      </c>
-      <c r="U101">
-        <v>0.0613</v>
-      </c>
-      <c r="V101">
-        <v>0.2</v>
-      </c>
-      <c r="W101">
-        <v>0.04904</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba1/BB+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.552726653923763</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
